--- a/4 четверть_19_JavaScript_vite.xlsx
+++ b/4 четверть_19_JavaScript_vite.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Machenike\Desktop\GB_Developer_Workbook\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AlexServHW\Desktop\GB_Developer_Workbook\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE05C4CB-C53D-413B-A916-B08BA403273C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0718363D-AD43-4C6C-BB6F-1F3BEAE625EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="14020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7080" yWindow="-19140" windowWidth="23250" windowHeight="12450" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="vite" sheetId="15" r:id="rId1"/>
@@ -20,12 +20,15 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="83">
   <si>
     <t>vite</t>
   </si>
@@ -612,18 +615,472 @@
   </si>
   <si>
     <t>Команды</t>
+  </si>
+  <si>
+    <t>Переменные окружения</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Примечание: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>--mode — это встроенная возможность Vite, а не отдельная библиотека. Это стандартный CLI-флаг, который Vite предоставляет "из коробки". Он устанавливает режим (mode) сборки.</t>
+    </r>
+  </si>
+  <si>
+    <t>"electronbuilddev": "vite build --mode electrondev",</t>
+  </si>
+  <si>
+    <t>.env.electrondev</t>
+  </si>
+  <si>
+    <t>VITE_ELECTRON_PROXY=1
+VITE_PAT_TO_BUILD= ./electron/renderer/dist/
+VITE_API_PROXY=http://127.0.0.1:9292
+VITE_SOCKET_PROXY=http://127.0.0.1:9092
+FILE_LOAD=https://mylk.hwcompany.ru</t>
+  </si>
+  <si>
+    <t>.env.electronprod</t>
+  </si>
+  <si>
+    <t>VITE_ELECTRON_PROXY=1
+VITE_PAT_TO_BUILD= ./electron/renderer/dist/
+VITE_API_PROXY=https://mylk.hwcompany.ru/api
+VITE_SOCKET_PROXY=https://mylk.hwcompany.ru</t>
+  </si>
+  <si>
+    <t>.env.test</t>
+  </si>
+  <si>
+    <t>NODE_ENV=production
+VITE_API_PROXY='/api'
+VITE_PAT_TO_BUILD= /srv/deploy/sites/test/</t>
+  </si>
+  <si>
+    <t>.env.development</t>
+  </si>
+  <si>
+    <t>NODE_ENV=development
+VITE_LOCALPROXY=1
+VITE_API_PROXY=http://127.0.0.1:9292
+VITE_SOCKET_PROXY=http://127.0.0.1:9092
+VITE_FILE_LOAD=http://127.0.0.1:9292
+VITE_CHART_KEY=2mA4mpE-11E2B4G1B3J3B3A2C3F3B4E4D4uddD7E4F4lD3C4D2ac1wE3A3B2qH-8jB1C4B1qkiB4D1A33A15B12A4D7A2B4A4H4nj1b1A7A3KE3tpgA1C3A4C-16mD2FH3H1F-7B-22tC8B2E6D2E2F2I2C10A2D1D6C1G2D3r==</t>
+  </si>
+  <si>
+    <t>.env.production</t>
+  </si>
+  <si>
+    <t>NODE_ENV=production
+VITE_API_PROXY='/api'
+VITE_PAT_TO_BUILD=../../../srv/www/sites/mylk/</t>
+  </si>
+  <si>
+    <t>Файлы .env</t>
+  </si>
+  <si>
+    <t>Доступ к переменным окружения в проекте</t>
+  </si>
+  <si>
+    <t>Часть 1</t>
+  </si>
+  <si>
+    <t>plugins/env.js</t>
+  </si>
+  <si>
+    <t>const EnvPlugin = {
+  install(Vue) {
+    Vue.prototype.$env = {
+      isLocalProxy: import.meta.env.VITE_LOCALPROXY,
+      isElectronProxy: import.meta.env.VITE_ELECTRON_PROXY,
+      pathToBuild: import.meta.env.VITE_PAT_TO_BUILD,
+      apiProxy: import.meta.env.VITE_API_PROXY,
+      socketProxy: import.meta.env.VITE_SOCKET_PROXY,
+      fileLoaderPath: import.meta.env.VITE_FILE_LOAD,
+    }
+  }
+}
+export default EnvPlugin</t>
+  </si>
+  <si>
+    <t>package.json</t>
+  </si>
+  <si>
+    <t>Часть 2</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">В vite package.json
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Важно! </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+  base: env.VITE_ELECTRON_PROXY ? './' : '/',
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Пояснение!</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> если правильно помню тут путь определяется относительно корневого index.html. В зависимости от того, где будет расположен index.html выбирается относительный или абсолютный путь навигации к остальным файлам собранного проекта</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">const { createVuePlugin } = require('vite-plugin-vue2');
+import { defineConfig, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>loadEnv</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> } from 'vite'
+import { nodePolyfills } from 'vite-plugin-node-polyfills';
+const path = require('path');
+import pluginRewriteAll from '@brrock/vite-plugin-rewrite-all';
+export default defineConfig(({ mode }) =&gt; {
+  // Загружаем переменные окружения
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">  const env = loadEnv(mode, process.cwd(), '')</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+  const isLocalProxy = </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>env.VITE_LOCALPROXY</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> === '1';
+ return {
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">  base: env.VITE_ELECTRON_PROXY ? './' : '/',
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">  plugins: [
+    createVuePlugin(),
+      pluginRewriteAll(),
+    nodePolyfills({ //ТРЕБУЕТСЯ для node.js модулей, встроенных в сторнние зависимости
+      globals: true,
+    })
+  ],
+  css: {
+    preprocessorOptions: {
+      scss: { silenceDeprecations: ['legacy-js-api', 'global-builtin','function-units','slash-div','import'] }
+    }
+  },
+  optimizeDeps: {
+    include: [
+      'lodash/debounce', 
+      'echarts/lib/echarts',
+    ]
+  },
+  build: {
+    outDir: env.VITE_PAT_TO_BUILD || 'dist',
+    assetsInlineLimit: 4096,
+  },
+  resolve: {
+    alias: {
+        'assets': path.resolve(__dirname, './src/assets'),
+        'components': path.resolve(__dirname, './src/components'),
+        'src': path.resolve(__dirname, './src'),
+        'vue': 'vue/dist/vue.esm.js',
+        '@': path.resolve(__dirname, './src'),
+        'sounds': path.resolve(__dirname, './public/sounds'),
+    }
+  },
+  server: isLocalProxy ? {
+      proxy: {
+        '/socket.io': {
+          target: env.VITE_SOCKET_PROXY,
+          ws: true
+        },
+        // '/exports': {
+        //    target: 'https://mylk.hwcompany.ru/',
+        //    secure: false,
+        //    changeOrigin: true
+        // }
+      },
+    } : {
+        port: 9390,
+        proxy: {
+            '/socket.io': {
+                ws: true
+            }
+        },
+        // historyApiFallback: true
+    },
+  };
+})
+</t>
+    </r>
+  </si>
+  <si>
+    <t>В остальных файлах</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>import Vue from "vue";</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+async getAllManagersFullNames(){
+            try {
+                this.loading = true;
+                const { body } = await this.$http.post(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Vue.prototype.$env.apiProxy</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> + '/mailingsettings/getAllManagersFullNames', {})
+                if (body) {
+                    this.allManagersFullNames = body;
+                }
+            } finally {
+                this.loading = false;
+            }
+        },</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">scripts": {
+    "dev": "vite --mode development",
+    "build": "export NODE_OPTIONS=--openssl-legacy-provider &amp;&amp; vite build </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>--mode production</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">",
+    "test": "export NODE_OPTIONS=--openssl-legacy-provider &amp;&amp; vite build </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>--mode test</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>",
+    "electronbuilddev": "vite build --mode electrondev",
+    "electronbuildprod": "vite build --mode electronprod",
+    "electron": "electron .",
+    "dist": "electron-builder --win --x64"
+  },</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -748,6 +1205,22 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF00B0F0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="7">
     <fill>
@@ -798,9 +1271,9 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -808,47 +1281,47 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="9" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="10" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="7" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="8" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="9" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="11" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
@@ -857,7 +1330,19 @@
     <xf numFmtId="49" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -876,6 +1361,55 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>167999</xdr:colOff>
+      <xdr:row>47</xdr:row>
+      <xdr:rowOff>58239</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1506668</xdr:colOff>
+      <xdr:row>47</xdr:row>
+      <xdr:rowOff>4853941</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Рисунок 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0FF858A1-FAC6-4C87-9EF6-DEEE19343400}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10985678" y="20414525"/>
+          <a:ext cx="1334859" cy="4799512"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1144,38 +1678,38 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:U105"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A2:U107"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="36" style="1" customWidth="1"/>
-    <col min="2" max="2" width="50.54296875" style="2" customWidth="1"/>
-    <col min="3" max="3" width="71.1796875" style="3" customWidth="1"/>
-    <col min="4" max="4" width="57.08984375" style="3" customWidth="1"/>
-    <col min="5" max="5" width="6.1796875" style="4" customWidth="1"/>
-    <col min="6" max="6" width="43.1796875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="55.08984375" style="2" customWidth="1"/>
-    <col min="8" max="8" width="67.90625" style="1" customWidth="1"/>
-    <col min="9" max="9" width="64.36328125" style="1" customWidth="1"/>
-    <col min="10" max="10" width="7.81640625" style="1" customWidth="1"/>
-    <col min="11" max="11" width="39.1796875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="48.90625" style="1" customWidth="1"/>
-    <col min="13" max="13" width="72.6328125" style="1" customWidth="1"/>
-    <col min="14" max="14" width="43.90625" style="1" customWidth="1"/>
-    <col min="15" max="15" width="7.81640625" style="1" customWidth="1"/>
-    <col min="16" max="16" width="56.81640625" style="2" customWidth="1"/>
-    <col min="17" max="17" width="46.81640625" style="2" customWidth="1"/>
-    <col min="18" max="18" width="62.90625" style="2" customWidth="1"/>
-    <col min="19" max="19" width="49.1796875" style="1" customWidth="1"/>
-    <col min="21" max="21" width="67.81640625" style="2" customWidth="1"/>
-    <col min="22" max="22" width="68.36328125" style="1" customWidth="1"/>
-    <col min="23" max="24" width="59.36328125" style="1" customWidth="1"/>
-    <col min="25" max="25" width="59.6328125" style="1" customWidth="1"/>
-    <col min="26" max="26" width="99.453125" style="1" customWidth="1"/>
-    <col min="27" max="27" width="41.1796875" style="1" customWidth="1"/>
-    <col min="28" max="16384" width="8.81640625" style="1"/>
+    <col min="2" max="2" width="50.5546875" style="2" customWidth="1"/>
+    <col min="3" max="3" width="71.21875" style="3" customWidth="1"/>
+    <col min="4" max="4" width="57.109375" style="3" customWidth="1"/>
+    <col min="5" max="5" width="6.21875" style="4" customWidth="1"/>
+    <col min="6" max="6" width="43.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="55.109375" style="2" customWidth="1"/>
+    <col min="8" max="8" width="67.88671875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="64.33203125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="7.77734375" style="1" customWidth="1"/>
+    <col min="11" max="11" width="39.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="48.88671875" style="1" customWidth="1"/>
+    <col min="13" max="13" width="72.6640625" style="1" customWidth="1"/>
+    <col min="14" max="14" width="43.88671875" style="1" customWidth="1"/>
+    <col min="15" max="15" width="7.77734375" style="1" customWidth="1"/>
+    <col min="16" max="16" width="56.77734375" style="2" customWidth="1"/>
+    <col min="17" max="17" width="46.77734375" style="2" customWidth="1"/>
+    <col min="18" max="18" width="62.88671875" style="2" customWidth="1"/>
+    <col min="19" max="19" width="49.21875" style="1" customWidth="1"/>
+    <col min="21" max="21" width="67.77734375" style="2" customWidth="1"/>
+    <col min="22" max="22" width="68.33203125" style="1" customWidth="1"/>
+    <col min="23" max="24" width="59.33203125" style="1" customWidth="1"/>
+    <col min="25" max="25" width="59.6640625" style="1" customWidth="1"/>
+    <col min="26" max="26" width="99.44140625" style="1" customWidth="1"/>
+    <col min="27" max="27" width="41.21875" style="1" customWidth="1"/>
+    <col min="28" max="16384" width="8.77734375" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:21" s="4" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:21" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B2" s="5"/>
       <c r="C2" s="6"/>
       <c r="D2" s="7"/>
@@ -1186,27 +1720,27 @@
       <c r="T2" s="9"/>
       <c r="U2" s="8"/>
     </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:21" x14ac:dyDescent="0.3">
       <c r="C3" s="11" t="s">
         <v>0</v>
       </c>
       <c r="S3" s="2"/>
     </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A4" s="14" t="s">
         <v>44</v>
       </c>
       <c r="C4" s="2"/>
       <c r="S4" s="2"/>
     </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A5" s="17" t="s">
         <v>53</v>
       </c>
       <c r="C5" s="2"/>
       <c r="S5" s="2"/>
     </row>
-    <row r="6" spans="1:21" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:21" ht="72" x14ac:dyDescent="0.3">
       <c r="A6" s="13" t="s">
         <v>49</v>
       </c>
@@ -1218,7 +1752,7 @@
       </c>
       <c r="S6" s="2"/>
     </row>
-    <row r="7" spans="1:21" ht="87" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:21" ht="86.4" x14ac:dyDescent="0.3">
       <c r="B7" s="13" t="s">
         <v>50</v>
       </c>
@@ -1230,7 +1764,7 @@
       </c>
       <c r="S7" s="2"/>
     </row>
-    <row r="8" spans="1:21" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:21" ht="43.2" x14ac:dyDescent="0.3">
       <c r="B8" s="2" t="s">
         <v>46</v>
       </c>
@@ -1239,14 +1773,14 @@
       </c>
       <c r="S8" s="2"/>
     </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A9" s="18" t="s">
         <v>54</v>
       </c>
       <c r="C9" s="2"/>
       <c r="S9" s="2"/>
     </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A10" s="2"/>
       <c r="B10" s="2" t="s">
         <v>56</v>
@@ -1256,14 +1790,14 @@
       </c>
       <c r="S10" s="2"/>
     </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A11" s="19" t="s">
         <v>57</v>
       </c>
       <c r="C11" s="16"/>
       <c r="S11" s="2"/>
     </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A12" s="20" t="s">
         <v>3</v>
       </c>
@@ -1271,7 +1805,7 @@
       <c r="D12" s="13"/>
       <c r="S12" s="2"/>
     </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A13" s="12"/>
       <c r="B13" s="12" t="s">
         <v>4</v>
@@ -1281,7 +1815,7 @@
       </c>
       <c r="D13" s="10"/>
     </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A14" s="10"/>
       <c r="B14" s="10" t="s">
         <v>9</v>
@@ -1291,7 +1825,7 @@
       </c>
       <c r="D14" s="10"/>
     </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A15" s="10"/>
       <c r="B15" s="10" t="s">
         <v>10</v>
@@ -1301,7 +1835,7 @@
       </c>
       <c r="D15" s="10"/>
     </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A16" s="10"/>
       <c r="B16" s="10" t="s">
         <v>11</v>
@@ -1311,7 +1845,7 @@
       </c>
       <c r="D16" s="10"/>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="10"/>
       <c r="B17" s="10" t="s">
         <v>12</v>
@@ -1321,7 +1855,7 @@
       </c>
       <c r="D17" s="10"/>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="10"/>
       <c r="B18" s="10" t="s">
         <v>13</v>
@@ -1331,7 +1865,7 @@
       </c>
       <c r="D18" s="10"/>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" s="10"/>
       <c r="B19" s="10" t="s">
         <v>14</v>
@@ -1341,7 +1875,7 @@
       </c>
       <c r="D19" s="10"/>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="10"/>
       <c r="B20" s="10" t="s">
         <v>15</v>
@@ -1351,7 +1885,7 @@
       </c>
       <c r="D20" s="10"/>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" s="10"/>
       <c r="B21" s="10" t="s">
         <v>16</v>
@@ -1361,7 +1895,7 @@
       </c>
       <c r="D21" s="10"/>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="10"/>
       <c r="B22" s="10" t="s">
         <v>17</v>
@@ -1371,7 +1905,7 @@
       </c>
       <c r="D22" s="10"/>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" s="10"/>
       <c r="B23" s="10" t="s">
         <v>18</v>
@@ -1381,7 +1915,7 @@
       </c>
       <c r="D23" s="10"/>
     </row>
-    <row r="24" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A24" s="10"/>
       <c r="B24" s="10" t="s">
         <v>19</v>
@@ -1391,7 +1925,7 @@
       </c>
       <c r="D24" s="10"/>
     </row>
-    <row r="25" spans="1:4" ht="58" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A25" s="10"/>
       <c r="B25" s="10" t="s">
         <v>20</v>
@@ -1403,7 +1937,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" s="10"/>
       <c r="B26" s="10" t="s">
         <v>22</v>
@@ -1413,7 +1947,7 @@
       </c>
       <c r="D26" s="10"/>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" s="10"/>
       <c r="B27" s="10" t="s">
         <v>23</v>
@@ -1423,7 +1957,7 @@
       </c>
       <c r="D27" s="10"/>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" s="10"/>
       <c r="B28" s="10" t="s">
         <v>24</v>
@@ -1433,7 +1967,7 @@
       </c>
       <c r="D28" s="10"/>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" s="10"/>
       <c r="B29" s="10" t="s">
         <v>25</v>
@@ -1443,7 +1977,7 @@
       </c>
       <c r="D29" s="10"/>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" s="10"/>
       <c r="B30" s="10" t="s">
         <v>27</v>
@@ -1453,7 +1987,7 @@
       </c>
       <c r="D30" s="10"/>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" s="10"/>
       <c r="B31" s="12" t="s">
         <v>4</v>
@@ -1461,7 +1995,7 @@
       <c r="C31" s="10"/>
       <c r="D31" s="10"/>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" s="20" t="s">
         <v>6</v>
       </c>
@@ -1473,7 +2007,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="33" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A33" s="10"/>
       <c r="B33" s="10"/>
       <c r="C33" s="12" t="s">
@@ -1481,7 +2015,7 @@
       </c>
       <c r="D33" s="10"/>
     </row>
-    <row r="34" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A34" s="10"/>
       <c r="B34" s="10"/>
       <c r="C34" s="12" t="s">
@@ -1489,435 +2023,502 @@
       </c>
       <c r="D34" s="10"/>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A35" s="10"/>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A35" s="22" t="s">
+        <v>58</v>
+      </c>
       <c r="B35" s="10"/>
       <c r="C35" s="10"/>
       <c r="D35" s="10"/>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A36" s="10"/>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A36" s="23" t="s">
+        <v>76</v>
+      </c>
       <c r="B36" s="10"/>
-      <c r="C36" s="10"/>
+      <c r="C36" s="1"/>
       <c r="D36" s="10"/>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:4" ht="158.4" x14ac:dyDescent="0.3">
       <c r="A37" s="10"/>
       <c r="B37" s="10"/>
-      <c r="C37" s="10"/>
+      <c r="C37" s="24" t="s">
+        <v>82</v>
+      </c>
       <c r="D37" s="10"/>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A38" s="10"/>
-      <c r="B38" s="10"/>
-      <c r="C38" s="10"/>
-      <c r="D38" s="10"/>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A39" s="10"/>
-      <c r="B39" s="10"/>
-      <c r="C39" s="10"/>
-      <c r="D39" s="10"/>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A40" s="10"/>
-      <c r="B40" s="10"/>
-      <c r="C40" s="10"/>
-      <c r="D40" s="10"/>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A41" s="10"/>
-      <c r="B41" s="10"/>
-      <c r="C41" s="10"/>
-      <c r="D41" s="10"/>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A42" s="10"/>
-      <c r="B42" s="10"/>
-      <c r="C42" s="10"/>
-      <c r="D42" s="10"/>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A43" s="10"/>
-      <c r="B43" s="10"/>
-      <c r="C43" s="10"/>
-      <c r="D43" s="10"/>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A44" s="10"/>
-      <c r="B44" s="10"/>
-      <c r="C44" s="10"/>
-      <c r="D44" s="10"/>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A45" s="10"/>
-      <c r="B45" s="10"/>
-      <c r="C45" s="10"/>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A38" s="23" t="s">
+        <v>71</v>
+      </c>
+      <c r="B38" s="21"/>
+      <c r="C38" s="21"/>
+      <c r="D38" s="21"/>
+    </row>
+    <row r="39" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A39" s="21"/>
+      <c r="B39" s="21" t="s">
+        <v>59</v>
+      </c>
+      <c r="C39" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="D39" s="21"/>
+    </row>
+    <row r="40" spans="1:4" ht="72" x14ac:dyDescent="0.3">
+      <c r="A40" s="21" t="s">
+        <v>61</v>
+      </c>
+      <c r="B40" s="21" t="s">
+        <v>58</v>
+      </c>
+      <c r="C40" s="21" t="s">
+        <v>62</v>
+      </c>
+      <c r="D40" s="21"/>
+    </row>
+    <row r="41" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A41" s="21" t="s">
+        <v>63</v>
+      </c>
+      <c r="B41" s="21"/>
+      <c r="C41" s="21" t="s">
+        <v>64</v>
+      </c>
+      <c r="D41" s="21"/>
+    </row>
+    <row r="42" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A42" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="B42" s="21"/>
+      <c r="C42" s="21" t="s">
+        <v>66</v>
+      </c>
+      <c r="D42" s="21"/>
+    </row>
+    <row r="43" spans="1:4" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="A43" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="B43" s="21"/>
+      <c r="C43" s="21" t="s">
+        <v>68</v>
+      </c>
+      <c r="D43" s="21"/>
+    </row>
+    <row r="44" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A44" s="21" t="s">
+        <v>69</v>
+      </c>
+      <c r="B44" s="21"/>
+      <c r="C44" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="D44" s="21"/>
+    </row>
+    <row r="45" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A45" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="B45" s="21" t="s">
+        <v>73</v>
+      </c>
+      <c r="C45" s="21"/>
       <c r="D45" s="10"/>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A46" s="10"/>
-      <c r="B46" s="10"/>
-      <c r="C46" s="10"/>
+    <row r="46" spans="1:4" ht="201.6" x14ac:dyDescent="0.3">
+      <c r="A46" s="21" t="s">
+        <v>74</v>
+      </c>
+      <c r="B46" s="21"/>
+      <c r="C46" s="21" t="s">
+        <v>75</v>
+      </c>
       <c r="D46" s="10"/>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A47" s="10"/>
-      <c r="B47" s="10"/>
-      <c r="C47" s="10"/>
-      <c r="D47" s="10"/>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A48" s="10"/>
-      <c r="B48" s="10"/>
-      <c r="C48" s="10"/>
-      <c r="D48" s="10"/>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A49" s="10"/>
-      <c r="B49" s="10"/>
-      <c r="C49" s="10"/>
-      <c r="D49" s="10"/>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A47" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="B47" s="21" t="s">
+        <v>77</v>
+      </c>
+      <c r="C47" s="21"/>
+      <c r="D47" s="21"/>
+    </row>
+    <row r="48" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A48" s="21"/>
+      <c r="B48" s="21" t="s">
+        <v>78</v>
+      </c>
+      <c r="C48" s="21" t="s">
+        <v>79</v>
+      </c>
+      <c r="D48" s="21"/>
+    </row>
+    <row r="49" spans="1:4" ht="201.6" x14ac:dyDescent="0.3">
+      <c r="A49" s="21"/>
+      <c r="B49" s="21" t="s">
+        <v>80</v>
+      </c>
+      <c r="C49" s="21" t="s">
+        <v>81</v>
+      </c>
+      <c r="D49" s="21"/>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A50" s="10"/>
       <c r="B50" s="10"/>
       <c r="C50" s="10"/>
       <c r="D50" s="10"/>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A51" s="10"/>
       <c r="B51" s="10"/>
       <c r="C51" s="10"/>
       <c r="D51" s="10"/>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A52" s="10"/>
       <c r="B52" s="10"/>
       <c r="C52" s="10"/>
       <c r="D52" s="10"/>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A53" s="10"/>
       <c r="B53" s="10"/>
       <c r="C53" s="10"/>
       <c r="D53" s="10"/>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A54" s="10"/>
       <c r="B54" s="10"/>
       <c r="C54" s="10"/>
       <c r="D54" s="10"/>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A55" s="10"/>
       <c r="B55" s="10"/>
       <c r="C55" s="10"/>
       <c r="D55" s="10"/>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A56" s="10"/>
       <c r="B56" s="10"/>
       <c r="C56" s="10"/>
       <c r="D56" s="10"/>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A57" s="10"/>
       <c r="B57" s="10"/>
       <c r="C57" s="10"/>
       <c r="D57" s="10"/>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A58" s="10"/>
       <c r="B58" s="10"/>
       <c r="C58" s="10"/>
       <c r="D58" s="10"/>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A59" s="10"/>
       <c r="B59" s="10"/>
       <c r="C59" s="10"/>
       <c r="D59" s="10"/>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A60" s="10"/>
       <c r="B60" s="10"/>
       <c r="C60" s="10"/>
       <c r="D60" s="10"/>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A61" s="10"/>
       <c r="B61" s="10"/>
       <c r="C61" s="10"/>
       <c r="D61" s="10"/>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A62" s="10"/>
       <c r="B62" s="10"/>
       <c r="C62" s="10"/>
       <c r="D62" s="10"/>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A63" s="10"/>
       <c r="B63" s="10"/>
       <c r="C63" s="10"/>
       <c r="D63" s="10"/>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A64" s="10"/>
       <c r="B64" s="10"/>
       <c r="C64" s="10"/>
       <c r="D64" s="10"/>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A65" s="10"/>
       <c r="B65" s="10"/>
       <c r="C65" s="10"/>
       <c r="D65" s="10"/>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A66" s="10"/>
       <c r="B66" s="10"/>
       <c r="C66" s="10"/>
       <c r="D66" s="10"/>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A67" s="10"/>
       <c r="B67" s="10"/>
       <c r="C67" s="10"/>
       <c r="D67" s="10"/>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A68" s="10"/>
       <c r="B68" s="10"/>
       <c r="C68" s="10"/>
       <c r="D68" s="10"/>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A69" s="10"/>
       <c r="B69" s="10"/>
       <c r="C69" s="10"/>
       <c r="D69" s="10"/>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A70" s="10"/>
       <c r="B70" s="10"/>
       <c r="C70" s="10"/>
       <c r="D70" s="10"/>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A71" s="10"/>
       <c r="B71" s="10"/>
       <c r="C71" s="10"/>
       <c r="D71" s="10"/>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A72" s="10"/>
       <c r="B72" s="10"/>
       <c r="C72" s="10"/>
       <c r="D72" s="10"/>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A73" s="10"/>
       <c r="B73" s="10"/>
       <c r="C73" s="10"/>
       <c r="D73" s="10"/>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A74" s="10"/>
       <c r="B74" s="10"/>
       <c r="C74" s="10"/>
       <c r="D74" s="10"/>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A75" s="10"/>
       <c r="B75" s="10"/>
       <c r="C75" s="10"/>
       <c r="D75" s="10"/>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A76" s="10"/>
       <c r="B76" s="10"/>
       <c r="C76" s="10"/>
       <c r="D76" s="10"/>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A77" s="10"/>
       <c r="B77" s="10"/>
       <c r="C77" s="10"/>
       <c r="D77" s="10"/>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A78" s="10"/>
       <c r="B78" s="10"/>
       <c r="C78" s="10"/>
       <c r="D78" s="10"/>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A79" s="10"/>
       <c r="B79" s="10"/>
       <c r="C79" s="10"/>
       <c r="D79" s="10"/>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A80" s="10"/>
       <c r="B80" s="10"/>
       <c r="C80" s="10"/>
       <c r="D80" s="10"/>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A81" s="10"/>
       <c r="B81" s="10"/>
       <c r="C81" s="10"/>
       <c r="D81" s="10"/>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A82" s="10"/>
       <c r="B82" s="10"/>
       <c r="C82" s="10"/>
       <c r="D82" s="10"/>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A83" s="10"/>
       <c r="B83" s="10"/>
       <c r="C83" s="10"/>
       <c r="D83" s="10"/>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A84" s="10"/>
       <c r="B84" s="10"/>
       <c r="C84" s="10"/>
       <c r="D84" s="10"/>
     </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A85" s="10"/>
       <c r="B85" s="10"/>
       <c r="C85" s="10"/>
       <c r="D85" s="10"/>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A86" s="10"/>
       <c r="B86" s="10"/>
       <c r="C86" s="10"/>
       <c r="D86" s="10"/>
     </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A87" s="10"/>
       <c r="B87" s="10"/>
       <c r="C87" s="10"/>
       <c r="D87" s="10"/>
     </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A88" s="10"/>
       <c r="B88" s="10"/>
       <c r="C88" s="10"/>
       <c r="D88" s="10"/>
     </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A89" s="10"/>
       <c r="B89" s="10"/>
       <c r="C89" s="10"/>
       <c r="D89" s="10"/>
     </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A90" s="10"/>
       <c r="B90" s="10"/>
       <c r="C90" s="10"/>
       <c r="D90" s="10"/>
     </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A91" s="10"/>
       <c r="B91" s="10"/>
       <c r="C91" s="10"/>
       <c r="D91" s="10"/>
     </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A92" s="10"/>
       <c r="B92" s="10"/>
       <c r="C92" s="10"/>
       <c r="D92" s="10"/>
     </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A93" s="10"/>
       <c r="B93" s="10"/>
       <c r="C93" s="10"/>
       <c r="D93" s="10"/>
     </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A94" s="10"/>
       <c r="B94" s="10"/>
       <c r="C94" s="10"/>
       <c r="D94" s="10"/>
     </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A95" s="10"/>
       <c r="B95" s="10"/>
       <c r="C95" s="10"/>
       <c r="D95" s="10"/>
     </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A96" s="10"/>
       <c r="B96" s="10"/>
       <c r="C96" s="10"/>
       <c r="D96" s="10"/>
     </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A97" s="10"/>
       <c r="B97" s="10"/>
       <c r="C97" s="10"/>
       <c r="D97" s="10"/>
     </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A98" s="10"/>
       <c r="B98" s="10"/>
       <c r="C98" s="10"/>
       <c r="D98" s="10"/>
     </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A99" s="10"/>
       <c r="B99" s="10"/>
       <c r="C99" s="10"/>
       <c r="D99" s="10"/>
     </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A100" s="10"/>
       <c r="B100" s="10"/>
       <c r="C100" s="10"/>
       <c r="D100" s="10"/>
     </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A101" s="10"/>
       <c r="B101" s="10"/>
       <c r="C101" s="10"/>
       <c r="D101" s="10"/>
     </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A102" s="10"/>
       <c r="B102" s="10"/>
       <c r="C102" s="10"/>
       <c r="D102" s="10"/>
     </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A103" s="10"/>
       <c r="B103" s="10"/>
       <c r="C103" s="10"/>
       <c r="D103" s="10"/>
     </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A104" s="10"/>
       <c r="B104" s="10"/>
       <c r="C104" s="10"/>
       <c r="D104" s="10"/>
     </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A105" s="10"/>
       <c r="B105" s="10"/>
       <c r="C105" s="10"/>
       <c r="D105" s="10"/>
     </row>
+    <row r="106" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A106" s="10"/>
+      <c r="B106" s="10"/>
+      <c r="C106" s="10"/>
+      <c r="D106" s="10"/>
+    </row>
+    <row r="107" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A107" s="10"/>
+      <c r="B107" s="10"/>
+      <c r="C107" s="10"/>
+      <c r="D107" s="10"/>
+    </row>
   </sheetData>
-  <phoneticPr fontId="15" type="noConversion"/>
+  <phoneticPr fontId="16" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="10" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/4 четверть_19_JavaScript_vite.xlsx
+++ b/4 четверть_19_JavaScript_vite.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AlexServHW\Desktop\GB_Developer_Workbook\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0718363D-AD43-4C6C-BB6F-1F3BEAE625EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C59F3806-5763-42E3-B667-51E75176E8B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7080" yWindow="-19140" windowWidth="23250" windowHeight="12450" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9900" yWindow="-16290" windowWidth="23250" windowHeight="12450" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="vite" sheetId="15" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="87">
   <si>
     <t>vite</t>
   </si>
@@ -1062,17 +1062,65 @@
   },</t>
     </r>
   </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Создать проект vite + </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>vue3</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Создать проект </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>vite + [...]</t>
+    </r>
+  </si>
+  <si>
+    <t>npm create vue@latest</t>
+  </si>
+  <si>
+    <t>`https://github.com/vuejs/create-vue</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="19" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1271,9 +1319,9 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -1281,47 +1329,47 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="10" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="11" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="8" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="9" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="10" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="6" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="12" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
@@ -1330,19 +1378,22 @@
     <xf numFmtId="49" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="6" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1369,14 +1420,14 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>167999</xdr:colOff>
-      <xdr:row>47</xdr:row>
+      <xdr:row>48</xdr:row>
       <xdr:rowOff>58239</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>1506668</xdr:colOff>
-      <xdr:row>47</xdr:row>
-      <xdr:rowOff>4853941</xdr:rowOff>
+      <xdr:colOff>1502858</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>4857751</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1678,7 +1729,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:U107"/>
+  <dimension ref="A2:U108"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="36" style="1" customWidth="1"/>
@@ -1752,19 +1803,23 @@
       </c>
       <c r="S6" s="2"/>
     </row>
-    <row r="7" spans="1:21" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="B7" s="13" t="s">
-        <v>50</v>
-      </c>
+    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B7" s="25"/>
       <c r="C7" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="D7" s="13" t="s">
-        <v>51</v>
+        <v>85</v>
+      </c>
+      <c r="D7" s="25" t="s">
+        <v>86</v>
       </c>
       <c r="S7" s="2"/>
     </row>
     <row r="8" spans="1:21" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
+        <v>84</v>
+      </c>
       <c r="B8" s="2" t="s">
         <v>46</v>
       </c>
@@ -1773,405 +1828,414 @@
       </c>
       <c r="S8" s="2"/>
     </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A9" s="18" t="s">
+    <row r="9" spans="1:21" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B9" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D9" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="S9" s="2"/>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A10" s="18" t="s">
         <v>54</v>
       </c>
-      <c r="C9" s="2"/>
-      <c r="S9" s="2"/>
-    </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A10" s="2"/>
-      <c r="B10" s="2" t="s">
+      <c r="C10" s="2"/>
+      <c r="S10" s="2"/>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A11" s="2"/>
+      <c r="B11" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="C10" s="16" t="s">
+      <c r="C11" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="S10" s="2"/>
-    </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A11" s="19" t="s">
+      <c r="S11" s="2"/>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A12" s="19" t="s">
         <v>57</v>
       </c>
-      <c r="C11" s="16"/>
-      <c r="S11" s="2"/>
-    </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A12" s="20" t="s">
+      <c r="C12" s="16"/>
+      <c r="S12" s="2"/>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A13" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="C12" s="15"/>
-      <c r="D12" s="13"/>
-      <c r="S12" s="2"/>
-    </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A13" s="12"/>
-      <c r="B13" s="12" t="s">
+      <c r="C13" s="15"/>
+      <c r="D13" s="13"/>
+      <c r="S13" s="2"/>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A14" s="12"/>
+      <c r="B14" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="C13" s="12" t="s">
+      <c r="C14" s="12" t="s">
         <v>8</v>
-      </c>
-      <c r="D13" s="10"/>
-    </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A14" s="10"/>
-      <c r="B14" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="C14" s="10" t="s">
-        <v>29</v>
       </c>
       <c r="D14" s="10"/>
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A15" s="10"/>
       <c r="B15" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>30</v>
+        <v>9</v>
+      </c>
+      <c r="C15" s="10" t="s">
+        <v>29</v>
       </c>
       <c r="D15" s="10"/>
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A16" s="10"/>
       <c r="B16" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="C16" s="10" t="s">
-        <v>31</v>
+        <v>10</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>30</v>
       </c>
       <c r="D16" s="10"/>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="10"/>
       <c r="B17" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D17" s="10"/>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="10"/>
       <c r="B18" s="10" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C18" s="10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D18" s="10"/>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" s="10"/>
       <c r="B19" s="10" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C19" s="10" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D19" s="10"/>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="10"/>
       <c r="B20" s="10" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C20" s="10" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D20" s="10"/>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" s="10"/>
       <c r="B21" s="10" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C21" s="10" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D21" s="10"/>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="10"/>
       <c r="B22" s="10" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C22" s="10" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D22" s="10"/>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" s="10"/>
       <c r="B23" s="10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C23" s="10" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D23" s="10"/>
     </row>
-    <row r="24" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" s="10"/>
       <c r="B24" s="10" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C24" s="10" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D24" s="10"/>
     </row>
-    <row r="25" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A25" s="10"/>
       <c r="B25" s="10" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C25" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="D25" s="12" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+        <v>39</v>
+      </c>
+      <c r="D25" s="10"/>
+    </row>
+    <row r="26" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A26" s="10"/>
       <c r="B26" s="10" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C26" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="D26" s="10"/>
+        <v>21</v>
+      </c>
+      <c r="D26" s="12" t="s">
+        <v>43</v>
+      </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" s="10"/>
       <c r="B27" s="10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C27" s="10" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D27" s="10"/>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" s="10"/>
       <c r="B28" s="10" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C28" s="10" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D28" s="10"/>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" s="10"/>
       <c r="B29" s="10" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C29" s="10" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="D29" s="10"/>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" s="10"/>
       <c r="B30" s="10" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C30" s="10" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D30" s="10"/>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" s="10"/>
-      <c r="B31" s="12" t="s">
+      <c r="B31" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="C31" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="D31" s="10"/>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A32" s="10"/>
+      <c r="B32" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="C31" s="10"/>
-      <c r="D31" s="10"/>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A32" s="20" t="s">
+      <c r="C32" s="10"/>
+      <c r="D32" s="10"/>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A33" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="B32" s="10"/>
-      <c r="C32" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="D32" s="12" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A33" s="10"/>
       <c r="B33" s="10"/>
       <c r="C33" s="12" t="s">
-        <v>1</v>
-      </c>
-      <c r="D33" s="10"/>
+        <v>7</v>
+      </c>
+      <c r="D33" s="12" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="34" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A34" s="10"/>
       <c r="B34" s="10"/>
       <c r="C34" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="D34" s="10"/>
+    </row>
+    <row r="35" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A35" s="10"/>
+      <c r="B35" s="10"/>
+      <c r="C35" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="D34" s="10"/>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A35" s="22" t="s">
+      <c r="D35" s="10"/>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A36" s="22" t="s">
         <v>58</v>
       </c>
-      <c r="B35" s="10"/>
-      <c r="C35" s="10"/>
-      <c r="D35" s="10"/>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A36" s="23" t="s">
+      <c r="B36" s="10"/>
+      <c r="C36" s="10"/>
+      <c r="D36" s="10"/>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A37" s="23" t="s">
         <v>76</v>
       </c>
-      <c r="B36" s="10"/>
-      <c r="C36" s="1"/>
-      <c r="D36" s="10"/>
-    </row>
-    <row r="37" spans="1:4" ht="158.4" x14ac:dyDescent="0.3">
-      <c r="A37" s="10"/>
       <c r="B37" s="10"/>
-      <c r="C37" s="24" t="s">
+      <c r="C37" s="1"/>
+      <c r="D37" s="10"/>
+    </row>
+    <row r="38" spans="1:4" ht="158.4" x14ac:dyDescent="0.3">
+      <c r="A38" s="10"/>
+      <c r="B38" s="10"/>
+      <c r="C38" s="24" t="s">
         <v>82</v>
       </c>
-      <c r="D37" s="10"/>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A38" s="23" t="s">
+      <c r="D38" s="10"/>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A39" s="23" t="s">
         <v>71</v>
       </c>
-      <c r="B38" s="21"/>
-      <c r="C38" s="21"/>
-      <c r="D38" s="21"/>
-    </row>
-    <row r="39" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A39" s="21"/>
-      <c r="B39" s="21" t="s">
+      <c r="B39" s="21"/>
+      <c r="C39" s="21"/>
+      <c r="D39" s="21"/>
+    </row>
+    <row r="40" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A40" s="21"/>
+      <c r="B40" s="21" t="s">
         <v>59</v>
       </c>
-      <c r="C39" s="21" t="s">
+      <c r="C40" s="21" t="s">
         <v>60</v>
       </c>
-      <c r="D39" s="21"/>
-    </row>
-    <row r="40" spans="1:4" ht="72" x14ac:dyDescent="0.3">
-      <c r="A40" s="21" t="s">
+      <c r="D40" s="21"/>
+    </row>
+    <row r="41" spans="1:4" ht="72" x14ac:dyDescent="0.3">
+      <c r="A41" s="21" t="s">
         <v>61</v>
       </c>
-      <c r="B40" s="21" t="s">
+      <c r="B41" s="21" t="s">
         <v>58</v>
       </c>
-      <c r="C40" s="21" t="s">
+      <c r="C41" s="21" t="s">
         <v>62</v>
       </c>
-      <c r="D40" s="21"/>
-    </row>
-    <row r="41" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A41" s="21" t="s">
+      <c r="D41" s="21"/>
+    </row>
+    <row r="42" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A42" s="21" t="s">
         <v>63</v>
-      </c>
-      <c r="B41" s="21"/>
-      <c r="C41" s="21" t="s">
-        <v>64</v>
-      </c>
-      <c r="D41" s="21"/>
-    </row>
-    <row r="42" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A42" s="21" t="s">
-        <v>65</v>
       </c>
       <c r="B42" s="21"/>
       <c r="C42" s="21" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D42" s="21"/>
     </row>
-    <row r="43" spans="1:4" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A43" s="21" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B43" s="21"/>
       <c r="C43" s="21" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D43" s="21"/>
     </row>
-    <row r="44" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:4" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A44" s="21" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B44" s="21"/>
       <c r="C44" s="21" t="s">
+        <v>68</v>
+      </c>
+      <c r="D44" s="21"/>
+    </row>
+    <row r="45" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A45" s="21" t="s">
+        <v>69</v>
+      </c>
+      <c r="B45" s="21"/>
+      <c r="C45" s="21" t="s">
         <v>70</v>
       </c>
-      <c r="D44" s="21"/>
-    </row>
-    <row r="45" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A45" s="23" t="s">
+      <c r="D45" s="21"/>
+    </row>
+    <row r="46" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A46" s="23" t="s">
         <v>72</v>
       </c>
-      <c r="B45" s="21" t="s">
+      <c r="B46" s="21" t="s">
         <v>73</v>
       </c>
-      <c r="C45" s="21"/>
-      <c r="D45" s="10"/>
-    </row>
-    <row r="46" spans="1:4" ht="201.6" x14ac:dyDescent="0.3">
-      <c r="A46" s="21" t="s">
+      <c r="C46" s="21"/>
+      <c r="D46" s="10"/>
+    </row>
+    <row r="47" spans="1:4" ht="201.6" x14ac:dyDescent="0.3">
+      <c r="A47" s="21" t="s">
         <v>74</v>
       </c>
-      <c r="B46" s="21"/>
-      <c r="C46" s="21" t="s">
+      <c r="B47" s="21"/>
+      <c r="C47" s="21" t="s">
         <v>75</v>
       </c>
-      <c r="D46" s="10"/>
-    </row>
-    <row r="47" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A47" s="23" t="s">
+      <c r="D47" s="10"/>
+    </row>
+    <row r="48" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A48" s="23" t="s">
         <v>72</v>
       </c>
-      <c r="B47" s="21" t="s">
+      <c r="B48" s="21" t="s">
         <v>77</v>
       </c>
-      <c r="C47" s="21"/>
-      <c r="D47" s="21"/>
-    </row>
-    <row r="48" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A48" s="21"/>
-      <c r="B48" s="21" t="s">
-        <v>78</v>
-      </c>
-      <c r="C48" s="21" t="s">
-        <v>79</v>
-      </c>
+      <c r="C48" s="21"/>
       <c r="D48" s="21"/>
     </row>
-    <row r="49" spans="1:4" ht="201.6" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A49" s="21"/>
       <c r="B49" s="21" t="s">
+        <v>78</v>
+      </c>
+      <c r="C49" s="21" t="s">
+        <v>79</v>
+      </c>
+      <c r="D49" s="21"/>
+    </row>
+    <row r="50" spans="1:4" ht="201.6" x14ac:dyDescent="0.3">
+      <c r="A50" s="21"/>
+      <c r="B50" s="21" t="s">
         <v>80</v>
       </c>
-      <c r="C49" s="21" t="s">
+      <c r="C50" s="21" t="s">
         <v>81</v>
       </c>
-      <c r="D49" s="21"/>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A50" s="10"/>
-      <c r="B50" s="10"/>
-      <c r="C50" s="10"/>
-      <c r="D50" s="10"/>
+      <c r="D50" s="21"/>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A51" s="10"/>
@@ -2515,8 +2579,14 @@
       <c r="C107" s="10"/>
       <c r="D107" s="10"/>
     </row>
+    <row r="108" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A108" s="10"/>
+      <c r="B108" s="10"/>
+      <c r="C108" s="10"/>
+      <c r="D108" s="10"/>
+    </row>
   </sheetData>
-  <phoneticPr fontId="16" type="noConversion"/>
+  <phoneticPr fontId="17" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="10" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
   <drawing r:id="rId2"/>

--- a/4 четверть_19_JavaScript_vite.xlsx
+++ b/4 четверть_19_JavaScript_vite.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AlexServHW\Desktop\GB_Developer_Workbook\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C59F3806-5763-42E3-B667-51E75176E8B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{251CF88E-FBC9-4741-AB0C-20012C812005}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9900" yWindow="-16290" windowWidth="23250" windowHeight="12450" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="vite" sheetId="15" r:id="rId1"/>
+    <sheet name="env" sheetId="16" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -1107,12 +1108,20 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="20" x14ac:knownFonts="1">
+  <fonts count="21" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1319,7 +1328,7 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -1329,47 +1338,47 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="12" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="8" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="9" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="10" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="11" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="13" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="6" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
@@ -1378,22 +1387,22 @@
     <xf numFmtId="49" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="7" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1420,13 +1429,13 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>167999</xdr:colOff>
-      <xdr:row>48</xdr:row>
+      <xdr:row>15</xdr:row>
       <xdr:rowOff>58239</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>1502858</xdr:colOff>
-      <xdr:row>48</xdr:row>
+      <xdr:row>15</xdr:row>
       <xdr:rowOff>4857751</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1434,7 +1443,7 @@
         <xdr:cNvPr id="2" name="Рисунок 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0FF858A1-FAC6-4C87-9EF6-DEEE19343400}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{06C482C2-7F52-4632-A676-8E793E7F6C03}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1450,7 +1459,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="10985678" y="20414525"/>
+          <a:off x="10988399" y="20540799"/>
           <a:ext cx="1334859" cy="4799512"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1729,7 +1738,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:U108"/>
+  <dimension ref="A2:U54"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="36" style="1" customWidth="1"/>
@@ -1807,11 +1816,11 @@
       <c r="A7" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="B7" s="25"/>
+      <c r="B7" s="24"/>
       <c r="C7" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="D7" s="25" t="s">
+      <c r="D7" s="24" t="s">
         <v>86</v>
       </c>
       <c r="S7" s="2"/>
@@ -2094,148 +2103,94 @@
       <c r="D35" s="10"/>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A36" s="22" t="s">
-        <v>58</v>
-      </c>
+      <c r="A36" s="10"/>
       <c r="B36" s="10"/>
       <c r="C36" s="10"/>
       <c r="D36" s="10"/>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A37" s="23" t="s">
-        <v>76</v>
-      </c>
+      <c r="A37" s="10"/>
       <c r="B37" s="10"/>
-      <c r="C37" s="1"/>
+      <c r="C37" s="10"/>
       <c r="D37" s="10"/>
     </row>
-    <row r="38" spans="1:4" ht="158.4" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38" s="10"/>
       <c r="B38" s="10"/>
-      <c r="C38" s="24" t="s">
-        <v>82</v>
-      </c>
+      <c r="C38" s="10"/>
       <c r="D38" s="10"/>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A39" s="23" t="s">
-        <v>71</v>
-      </c>
-      <c r="B39" s="21"/>
-      <c r="C39" s="21"/>
-      <c r="D39" s="21"/>
-    </row>
-    <row r="40" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A40" s="21"/>
-      <c r="B40" s="21" t="s">
-        <v>59</v>
-      </c>
-      <c r="C40" s="21" t="s">
-        <v>60</v>
-      </c>
-      <c r="D40" s="21"/>
-    </row>
-    <row r="41" spans="1:4" ht="72" x14ac:dyDescent="0.3">
-      <c r="A41" s="21" t="s">
-        <v>61</v>
-      </c>
-      <c r="B41" s="21" t="s">
-        <v>58</v>
-      </c>
-      <c r="C41" s="21" t="s">
-        <v>62</v>
-      </c>
-      <c r="D41" s="21"/>
-    </row>
-    <row r="42" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A42" s="21" t="s">
-        <v>63</v>
-      </c>
-      <c r="B42" s="21"/>
-      <c r="C42" s="21" t="s">
-        <v>64</v>
-      </c>
-      <c r="D42" s="21"/>
-    </row>
-    <row r="43" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A43" s="21" t="s">
-        <v>65</v>
-      </c>
-      <c r="B43" s="21"/>
-      <c r="C43" s="21" t="s">
-        <v>66</v>
-      </c>
-      <c r="D43" s="21"/>
-    </row>
-    <row r="44" spans="1:4" ht="129.6" x14ac:dyDescent="0.3">
-      <c r="A44" s="21" t="s">
-        <v>67</v>
-      </c>
-      <c r="B44" s="21"/>
-      <c r="C44" s="21" t="s">
-        <v>68</v>
-      </c>
-      <c r="D44" s="21"/>
-    </row>
-    <row r="45" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A45" s="21" t="s">
-        <v>69</v>
-      </c>
-      <c r="B45" s="21"/>
-      <c r="C45" s="21" t="s">
-        <v>70</v>
-      </c>
-      <c r="D45" s="21"/>
-    </row>
-    <row r="46" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A46" s="23" t="s">
-        <v>72</v>
-      </c>
-      <c r="B46" s="21" t="s">
-        <v>73</v>
-      </c>
-      <c r="C46" s="21"/>
+      <c r="A39" s="10"/>
+      <c r="B39" s="10"/>
+      <c r="C39" s="10"/>
+      <c r="D39" s="10"/>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A40" s="10"/>
+      <c r="B40" s="10"/>
+      <c r="C40" s="10"/>
+      <c r="D40" s="10"/>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A41" s="10"/>
+      <c r="B41" s="10"/>
+      <c r="C41" s="10"/>
+      <c r="D41" s="10"/>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A42" s="10"/>
+      <c r="B42" s="10"/>
+      <c r="C42" s="10"/>
+      <c r="D42" s="10"/>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A43" s="10"/>
+      <c r="B43" s="10"/>
+      <c r="C43" s="10"/>
+      <c r="D43" s="10"/>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A44" s="10"/>
+      <c r="B44" s="10"/>
+      <c r="C44" s="10"/>
+      <c r="D44" s="10"/>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A45" s="10"/>
+      <c r="B45" s="10"/>
+      <c r="C45" s="10"/>
+      <c r="D45" s="10"/>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A46" s="10"/>
+      <c r="B46" s="10"/>
+      <c r="C46" s="10"/>
       <c r="D46" s="10"/>
     </row>
-    <row r="47" spans="1:4" ht="201.6" x14ac:dyDescent="0.3">
-      <c r="A47" s="21" t="s">
-        <v>74</v>
-      </c>
-      <c r="B47" s="21"/>
-      <c r="C47" s="21" t="s">
-        <v>75</v>
-      </c>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A47" s="10"/>
+      <c r="B47" s="10"/>
+      <c r="C47" s="10"/>
       <c r="D47" s="10"/>
     </row>
-    <row r="48" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A48" s="23" t="s">
-        <v>72</v>
-      </c>
-      <c r="B48" s="21" t="s">
-        <v>77</v>
-      </c>
-      <c r="C48" s="21"/>
-      <c r="D48" s="21"/>
-    </row>
-    <row r="49" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A49" s="21"/>
-      <c r="B49" s="21" t="s">
-        <v>78</v>
-      </c>
-      <c r="C49" s="21" t="s">
-        <v>79</v>
-      </c>
-      <c r="D49" s="21"/>
-    </row>
-    <row r="50" spans="1:4" ht="201.6" x14ac:dyDescent="0.3">
-      <c r="A50" s="21"/>
-      <c r="B50" s="21" t="s">
-        <v>80</v>
-      </c>
-      <c r="C50" s="21" t="s">
-        <v>81</v>
-      </c>
-      <c r="D50" s="21"/>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A48" s="10"/>
+      <c r="B48" s="10"/>
+      <c r="C48" s="10"/>
+      <c r="D48" s="10"/>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A49" s="10"/>
+      <c r="B49" s="10"/>
+      <c r="C49" s="10"/>
+      <c r="D49" s="10"/>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A50" s="10"/>
+      <c r="B50" s="10"/>
+      <c r="C50" s="10"/>
+      <c r="D50" s="10"/>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A51" s="10"/>
@@ -2261,332 +2216,2135 @@
       <c r="C54" s="10"/>
       <c r="D54" s="10"/>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
+  </sheetData>
+  <phoneticPr fontId="18" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="10" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1958CFF-75BD-4DE9-A6BC-2C4CD3483EC9}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A2:AA75"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="36" style="1" customWidth="1"/>
+    <col min="2" max="2" width="50.5546875" style="2" customWidth="1"/>
+    <col min="3" max="3" width="71.21875" style="3" customWidth="1"/>
+    <col min="4" max="4" width="57.109375" style="3" customWidth="1"/>
+    <col min="5" max="5" width="6.21875" style="4" customWidth="1"/>
+    <col min="6" max="6" width="43.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="55.109375" style="2" customWidth="1"/>
+    <col min="8" max="8" width="67.88671875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="64.33203125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="7.77734375" style="1" customWidth="1"/>
+    <col min="11" max="11" width="39.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="48.88671875" style="1" customWidth="1"/>
+    <col min="13" max="13" width="72.6640625" style="1" customWidth="1"/>
+    <col min="14" max="14" width="43.88671875" style="1" customWidth="1"/>
+    <col min="15" max="15" width="7.77734375" style="1" customWidth="1"/>
+    <col min="16" max="16" width="56.77734375" style="2" customWidth="1"/>
+    <col min="17" max="17" width="46.77734375" style="2" customWidth="1"/>
+    <col min="18" max="18" width="62.88671875" style="2" customWidth="1"/>
+    <col min="19" max="19" width="49.21875" style="1" customWidth="1"/>
+    <col min="21" max="21" width="67.77734375" style="2" customWidth="1"/>
+    <col min="22" max="22" width="68.33203125" style="1" customWidth="1"/>
+    <col min="23" max="24" width="59.33203125" style="1" customWidth="1"/>
+    <col min="25" max="25" width="59.6640625" style="1" customWidth="1"/>
+    <col min="26" max="26" width="99.44140625" style="1" customWidth="1"/>
+    <col min="27" max="27" width="41.21875" style="1" customWidth="1"/>
+    <col min="28" max="16384" width="8.77734375" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="5"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="7"/>
+      <c r="G2" s="8"/>
+      <c r="P2" s="8"/>
+      <c r="Q2" s="8"/>
+      <c r="R2" s="8"/>
+      <c r="T2" s="9"/>
+      <c r="U2" s="8"/>
+    </row>
+    <row r="3" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="C3" s="25" t="s">
+        <v>58</v>
+      </c>
+      <c r="S3" s="2"/>
+    </row>
+    <row r="4" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="22" t="s">
+        <v>76</v>
+      </c>
+      <c r="B4" s="10"/>
+      <c r="C4" s="1"/>
+      <c r="D4" s="10"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="1"/>
+      <c r="I4" s="1"/>
+      <c r="J4" s="1"/>
+      <c r="K4" s="1"/>
+      <c r="L4" s="1"/>
+      <c r="M4" s="1"/>
+      <c r="N4" s="1"/>
+      <c r="O4" s="1"/>
+      <c r="P4" s="2"/>
+      <c r="Q4" s="2"/>
+      <c r="R4" s="2"/>
+      <c r="S4" s="1"/>
+      <c r="T4"/>
+      <c r="U4" s="2"/>
+      <c r="V4" s="1"/>
+      <c r="W4" s="1"/>
+      <c r="X4" s="1"/>
+      <c r="Y4" s="1"/>
+      <c r="Z4" s="1"/>
+      <c r="AA4" s="1"/>
+    </row>
+    <row r="5" spans="1:27" s="4" customFormat="1" ht="158.4" x14ac:dyDescent="0.3">
+      <c r="A5" s="10"/>
+      <c r="B5" s="10"/>
+      <c r="C5" s="23" t="s">
+        <v>82</v>
+      </c>
+      <c r="D5" s="10"/>
+      <c r="F5" s="1"/>
+      <c r="G5" s="2"/>
+      <c r="H5" s="1"/>
+      <c r="I5" s="1"/>
+      <c r="J5" s="1"/>
+      <c r="K5" s="1"/>
+      <c r="L5" s="1"/>
+      <c r="M5" s="1"/>
+      <c r="N5" s="1"/>
+      <c r="O5" s="1"/>
+      <c r="P5" s="2"/>
+      <c r="Q5" s="2"/>
+      <c r="R5" s="2"/>
+      <c r="S5" s="1"/>
+      <c r="T5"/>
+      <c r="U5" s="2"/>
+      <c r="V5" s="1"/>
+      <c r="W5" s="1"/>
+      <c r="X5" s="1"/>
+      <c r="Y5" s="1"/>
+      <c r="Z5" s="1"/>
+      <c r="AA5" s="1"/>
+    </row>
+    <row r="6" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="22" t="s">
+        <v>71</v>
+      </c>
+      <c r="B6" s="21"/>
+      <c r="C6" s="21"/>
+      <c r="D6" s="21"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="2"/>
+      <c r="H6" s="1"/>
+      <c r="I6" s="1"/>
+      <c r="J6" s="1"/>
+      <c r="K6" s="1"/>
+      <c r="L6" s="1"/>
+      <c r="M6" s="1"/>
+      <c r="N6" s="1"/>
+      <c r="O6" s="1"/>
+      <c r="P6" s="2"/>
+      <c r="Q6" s="2"/>
+      <c r="R6" s="2"/>
+      <c r="S6" s="1"/>
+      <c r="T6"/>
+      <c r="U6" s="2"/>
+      <c r="V6" s="1"/>
+      <c r="W6" s="1"/>
+      <c r="X6" s="1"/>
+      <c r="Y6" s="1"/>
+      <c r="Z6" s="1"/>
+      <c r="AA6" s="1"/>
+    </row>
+    <row r="7" spans="1:27" s="4" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A7" s="21"/>
+      <c r="B7" s="21" t="s">
+        <v>59</v>
+      </c>
+      <c r="C7" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="D7" s="21"/>
+      <c r="F7" s="1"/>
+      <c r="G7" s="2"/>
+      <c r="H7" s="1"/>
+      <c r="I7" s="1"/>
+      <c r="J7" s="1"/>
+      <c r="K7" s="1"/>
+      <c r="L7" s="1"/>
+      <c r="M7" s="1"/>
+      <c r="N7" s="1"/>
+      <c r="O7" s="1"/>
+      <c r="P7" s="2"/>
+      <c r="Q7" s="2"/>
+      <c r="R7" s="2"/>
+      <c r="S7" s="1"/>
+      <c r="T7"/>
+      <c r="U7" s="2"/>
+      <c r="V7" s="1"/>
+      <c r="W7" s="1"/>
+      <c r="X7" s="1"/>
+      <c r="Y7" s="1"/>
+      <c r="Z7" s="1"/>
+      <c r="AA7" s="1"/>
+    </row>
+    <row r="8" spans="1:27" s="4" customFormat="1" ht="72" x14ac:dyDescent="0.3">
+      <c r="A8" s="21" t="s">
+        <v>61</v>
+      </c>
+      <c r="B8" s="21" t="s">
+        <v>58</v>
+      </c>
+      <c r="C8" s="21" t="s">
+        <v>62</v>
+      </c>
+      <c r="D8" s="21"/>
+      <c r="F8" s="1"/>
+      <c r="G8" s="2"/>
+      <c r="H8" s="1"/>
+      <c r="I8" s="1"/>
+      <c r="J8" s="1"/>
+      <c r="K8" s="1"/>
+      <c r="L8" s="1"/>
+      <c r="M8" s="1"/>
+      <c r="N8" s="1"/>
+      <c r="O8" s="1"/>
+      <c r="P8" s="2"/>
+      <c r="Q8" s="2"/>
+      <c r="R8" s="2"/>
+      <c r="S8" s="1"/>
+      <c r="T8"/>
+      <c r="U8" s="2"/>
+      <c r="V8" s="1"/>
+      <c r="W8" s="1"/>
+      <c r="X8" s="1"/>
+      <c r="Y8" s="1"/>
+      <c r="Z8" s="1"/>
+      <c r="AA8" s="1"/>
+    </row>
+    <row r="9" spans="1:27" s="4" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A9" s="21" t="s">
+        <v>63</v>
+      </c>
+      <c r="B9" s="21"/>
+      <c r="C9" s="21" t="s">
+        <v>64</v>
+      </c>
+      <c r="D9" s="21"/>
+      <c r="F9" s="1"/>
+      <c r="G9" s="2"/>
+      <c r="H9" s="1"/>
+      <c r="I9" s="1"/>
+      <c r="J9" s="1"/>
+      <c r="K9" s="1"/>
+      <c r="L9" s="1"/>
+      <c r="M9" s="1"/>
+      <c r="N9" s="1"/>
+      <c r="O9" s="1"/>
+      <c r="P9" s="2"/>
+      <c r="Q9" s="2"/>
+      <c r="R9" s="2"/>
+      <c r="S9" s="1"/>
+      <c r="T9"/>
+      <c r="U9" s="2"/>
+      <c r="V9" s="1"/>
+      <c r="W9" s="1"/>
+      <c r="X9" s="1"/>
+      <c r="Y9" s="1"/>
+      <c r="Z9" s="1"/>
+      <c r="AA9" s="1"/>
+    </row>
+    <row r="10" spans="1:27" s="4" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A10" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="B10" s="21"/>
+      <c r="C10" s="21" t="s">
+        <v>66</v>
+      </c>
+      <c r="D10" s="21"/>
+      <c r="F10" s="1"/>
+      <c r="G10" s="2"/>
+      <c r="H10" s="1"/>
+      <c r="I10" s="1"/>
+      <c r="J10" s="1"/>
+      <c r="K10" s="1"/>
+      <c r="L10" s="1"/>
+      <c r="M10" s="1"/>
+      <c r="N10" s="1"/>
+      <c r="O10" s="1"/>
+      <c r="P10" s="2"/>
+      <c r="Q10" s="2"/>
+      <c r="R10" s="2"/>
+      <c r="S10" s="1"/>
+      <c r="T10"/>
+      <c r="U10" s="2"/>
+      <c r="V10" s="1"/>
+      <c r="W10" s="1"/>
+      <c r="X10" s="1"/>
+      <c r="Y10" s="1"/>
+      <c r="Z10" s="1"/>
+      <c r="AA10" s="1"/>
+    </row>
+    <row r="11" spans="1:27" s="4" customFormat="1" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="A11" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="B11" s="21"/>
+      <c r="C11" s="21" t="s">
+        <v>68</v>
+      </c>
+      <c r="D11" s="21"/>
+      <c r="F11" s="1"/>
+      <c r="G11" s="2"/>
+      <c r="H11" s="1"/>
+      <c r="I11" s="1"/>
+      <c r="J11" s="1"/>
+      <c r="K11" s="1"/>
+      <c r="L11" s="1"/>
+      <c r="M11" s="1"/>
+      <c r="N11" s="1"/>
+      <c r="O11" s="1"/>
+      <c r="P11" s="2"/>
+      <c r="Q11" s="2"/>
+      <c r="R11" s="2"/>
+      <c r="S11" s="1"/>
+      <c r="T11"/>
+      <c r="U11" s="2"/>
+      <c r="V11" s="1"/>
+      <c r="W11" s="1"/>
+      <c r="X11" s="1"/>
+      <c r="Y11" s="1"/>
+      <c r="Z11" s="1"/>
+      <c r="AA11" s="1"/>
+    </row>
+    <row r="12" spans="1:27" s="4" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A12" s="21" t="s">
+        <v>69</v>
+      </c>
+      <c r="B12" s="21"/>
+      <c r="C12" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="D12" s="21"/>
+      <c r="F12" s="1"/>
+      <c r="G12" s="2"/>
+      <c r="H12" s="1"/>
+      <c r="I12" s="1"/>
+      <c r="J12" s="1"/>
+      <c r="K12" s="1"/>
+      <c r="L12" s="1"/>
+      <c r="M12" s="1"/>
+      <c r="N12" s="1"/>
+      <c r="O12" s="1"/>
+      <c r="P12" s="2"/>
+      <c r="Q12" s="2"/>
+      <c r="R12" s="2"/>
+      <c r="S12" s="1"/>
+      <c r="T12"/>
+      <c r="U12" s="2"/>
+      <c r="V12" s="1"/>
+      <c r="W12" s="1"/>
+      <c r="X12" s="1"/>
+      <c r="Y12" s="1"/>
+      <c r="Z12" s="1"/>
+      <c r="AA12" s="1"/>
+    </row>
+    <row r="13" spans="1:27" s="4" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A13" s="22" t="s">
+        <v>72</v>
+      </c>
+      <c r="B13" s="21" t="s">
+        <v>73</v>
+      </c>
+      <c r="C13" s="21"/>
+      <c r="D13" s="10"/>
+      <c r="F13" s="1"/>
+      <c r="G13" s="2"/>
+      <c r="H13" s="1"/>
+      <c r="I13" s="1"/>
+      <c r="J13" s="1"/>
+      <c r="K13" s="1"/>
+      <c r="L13" s="1"/>
+      <c r="M13" s="1"/>
+      <c r="N13" s="1"/>
+      <c r="O13" s="1"/>
+      <c r="P13" s="2"/>
+      <c r="Q13" s="2"/>
+      <c r="R13" s="2"/>
+      <c r="S13" s="1"/>
+      <c r="T13"/>
+      <c r="U13" s="2"/>
+      <c r="V13" s="1"/>
+      <c r="W13" s="1"/>
+      <c r="X13" s="1"/>
+      <c r="Y13" s="1"/>
+      <c r="Z13" s="1"/>
+      <c r="AA13" s="1"/>
+    </row>
+    <row r="14" spans="1:27" s="4" customFormat="1" ht="201.6" x14ac:dyDescent="0.3">
+      <c r="A14" s="21" t="s">
+        <v>74</v>
+      </c>
+      <c r="B14" s="21"/>
+      <c r="C14" s="21" t="s">
+        <v>75</v>
+      </c>
+      <c r="D14" s="10"/>
+      <c r="F14" s="1"/>
+      <c r="G14" s="2"/>
+      <c r="H14" s="1"/>
+      <c r="I14" s="1"/>
+      <c r="J14" s="1"/>
+      <c r="K14" s="1"/>
+      <c r="L14" s="1"/>
+      <c r="M14" s="1"/>
+      <c r="N14" s="1"/>
+      <c r="O14" s="1"/>
+      <c r="P14" s="2"/>
+      <c r="Q14" s="2"/>
+      <c r="R14" s="2"/>
+      <c r="S14" s="1"/>
+      <c r="T14"/>
+      <c r="U14" s="2"/>
+      <c r="V14" s="1"/>
+      <c r="W14" s="1"/>
+      <c r="X14" s="1"/>
+      <c r="Y14" s="1"/>
+      <c r="Z14" s="1"/>
+      <c r="AA14" s="1"/>
+    </row>
+    <row r="15" spans="1:27" s="4" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A15" s="22" t="s">
+        <v>72</v>
+      </c>
+      <c r="B15" s="21" t="s">
+        <v>77</v>
+      </c>
+      <c r="C15" s="21"/>
+      <c r="D15" s="21"/>
+      <c r="F15" s="1"/>
+      <c r="G15" s="2"/>
+      <c r="H15" s="1"/>
+      <c r="I15" s="1"/>
+      <c r="J15" s="1"/>
+      <c r="K15" s="1"/>
+      <c r="L15" s="1"/>
+      <c r="M15" s="1"/>
+      <c r="N15" s="1"/>
+      <c r="O15" s="1"/>
+      <c r="P15" s="2"/>
+      <c r="Q15" s="2"/>
+      <c r="R15" s="2"/>
+      <c r="S15" s="1"/>
+      <c r="T15"/>
+      <c r="U15" s="2"/>
+      <c r="V15" s="1"/>
+      <c r="W15" s="1"/>
+      <c r="X15" s="1"/>
+      <c r="Y15" s="1"/>
+      <c r="Z15" s="1"/>
+      <c r="AA15" s="1"/>
+    </row>
+    <row r="16" spans="1:27" s="4" customFormat="1" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A16" s="21"/>
+      <c r="B16" s="21" t="s">
+        <v>78</v>
+      </c>
+      <c r="C16" s="21" t="s">
+        <v>79</v>
+      </c>
+      <c r="D16" s="21"/>
+      <c r="F16" s="1"/>
+      <c r="G16" s="2"/>
+      <c r="H16" s="1"/>
+      <c r="I16" s="1"/>
+      <c r="J16" s="1"/>
+      <c r="K16" s="1"/>
+      <c r="L16" s="1"/>
+      <c r="M16" s="1"/>
+      <c r="N16" s="1"/>
+      <c r="O16" s="1"/>
+      <c r="P16" s="2"/>
+      <c r="Q16" s="2"/>
+      <c r="R16" s="2"/>
+      <c r="S16" s="1"/>
+      <c r="T16"/>
+      <c r="U16" s="2"/>
+      <c r="V16" s="1"/>
+      <c r="W16" s="1"/>
+      <c r="X16" s="1"/>
+      <c r="Y16" s="1"/>
+      <c r="Z16" s="1"/>
+      <c r="AA16" s="1"/>
+    </row>
+    <row r="17" spans="1:27" s="4" customFormat="1" ht="201.6" x14ac:dyDescent="0.3">
+      <c r="A17" s="21"/>
+      <c r="B17" s="21" t="s">
+        <v>80</v>
+      </c>
+      <c r="C17" s="21" t="s">
+        <v>81</v>
+      </c>
+      <c r="D17" s="21"/>
+      <c r="F17" s="1"/>
+      <c r="G17" s="2"/>
+      <c r="H17" s="1"/>
+      <c r="I17" s="1"/>
+      <c r="J17" s="1"/>
+      <c r="K17" s="1"/>
+      <c r="L17" s="1"/>
+      <c r="M17" s="1"/>
+      <c r="N17" s="1"/>
+      <c r="O17" s="1"/>
+      <c r="P17" s="2"/>
+      <c r="Q17" s="2"/>
+      <c r="R17" s="2"/>
+      <c r="S17" s="1"/>
+      <c r="T17"/>
+      <c r="U17" s="2"/>
+      <c r="V17" s="1"/>
+      <c r="W17" s="1"/>
+      <c r="X17" s="1"/>
+      <c r="Y17" s="1"/>
+      <c r="Z17" s="1"/>
+      <c r="AA17" s="1"/>
+    </row>
+    <row r="18" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="10"/>
+      <c r="B18" s="10"/>
+      <c r="C18" s="10"/>
+      <c r="D18" s="10"/>
+      <c r="F18" s="1"/>
+      <c r="G18" s="2"/>
+      <c r="H18" s="1"/>
+      <c r="I18" s="1"/>
+      <c r="J18" s="1"/>
+      <c r="K18" s="1"/>
+      <c r="L18" s="1"/>
+      <c r="M18" s="1"/>
+      <c r="N18" s="1"/>
+      <c r="O18" s="1"/>
+      <c r="P18" s="2"/>
+      <c r="Q18" s="2"/>
+      <c r="R18" s="2"/>
+      <c r="S18" s="1"/>
+      <c r="T18"/>
+      <c r="U18" s="2"/>
+      <c r="V18" s="1"/>
+      <c r="W18" s="1"/>
+      <c r="X18" s="1"/>
+      <c r="Y18" s="1"/>
+      <c r="Z18" s="1"/>
+      <c r="AA18" s="1"/>
+    </row>
+    <row r="19" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="10"/>
+      <c r="B19" s="10"/>
+      <c r="C19" s="10"/>
+      <c r="D19" s="10"/>
+      <c r="F19" s="1"/>
+      <c r="G19" s="2"/>
+      <c r="H19" s="1"/>
+      <c r="I19" s="1"/>
+      <c r="J19" s="1"/>
+      <c r="K19" s="1"/>
+      <c r="L19" s="1"/>
+      <c r="M19" s="1"/>
+      <c r="N19" s="1"/>
+      <c r="O19" s="1"/>
+      <c r="P19" s="2"/>
+      <c r="Q19" s="2"/>
+      <c r="R19" s="2"/>
+      <c r="S19" s="1"/>
+      <c r="T19"/>
+      <c r="U19" s="2"/>
+      <c r="V19" s="1"/>
+      <c r="W19" s="1"/>
+      <c r="X19" s="1"/>
+      <c r="Y19" s="1"/>
+      <c r="Z19" s="1"/>
+      <c r="AA19" s="1"/>
+    </row>
+    <row r="20" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="10"/>
+      <c r="B20" s="10"/>
+      <c r="C20" s="10"/>
+      <c r="D20" s="10"/>
+      <c r="F20" s="1"/>
+      <c r="G20" s="2"/>
+      <c r="H20" s="1"/>
+      <c r="I20" s="1"/>
+      <c r="J20" s="1"/>
+      <c r="K20" s="1"/>
+      <c r="L20" s="1"/>
+      <c r="M20" s="1"/>
+      <c r="N20" s="1"/>
+      <c r="O20" s="1"/>
+      <c r="P20" s="2"/>
+      <c r="Q20" s="2"/>
+      <c r="R20" s="2"/>
+      <c r="S20" s="1"/>
+      <c r="T20"/>
+      <c r="U20" s="2"/>
+      <c r="V20" s="1"/>
+      <c r="W20" s="1"/>
+      <c r="X20" s="1"/>
+      <c r="Y20" s="1"/>
+      <c r="Z20" s="1"/>
+      <c r="AA20" s="1"/>
+    </row>
+    <row r="21" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="10"/>
+      <c r="B21" s="10"/>
+      <c r="C21" s="10"/>
+      <c r="D21" s="10"/>
+      <c r="F21" s="1"/>
+      <c r="G21" s="2"/>
+      <c r="H21" s="1"/>
+      <c r="I21" s="1"/>
+      <c r="J21" s="1"/>
+      <c r="K21" s="1"/>
+      <c r="L21" s="1"/>
+      <c r="M21" s="1"/>
+      <c r="N21" s="1"/>
+      <c r="O21" s="1"/>
+      <c r="P21" s="2"/>
+      <c r="Q21" s="2"/>
+      <c r="R21" s="2"/>
+      <c r="S21" s="1"/>
+      <c r="T21"/>
+      <c r="U21" s="2"/>
+      <c r="V21" s="1"/>
+      <c r="W21" s="1"/>
+      <c r="X21" s="1"/>
+      <c r="Y21" s="1"/>
+      <c r="Z21" s="1"/>
+      <c r="AA21" s="1"/>
+    </row>
+    <row r="22" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="10"/>
+      <c r="B22" s="10"/>
+      <c r="C22" s="10"/>
+      <c r="D22" s="10"/>
+      <c r="F22" s="1"/>
+      <c r="G22" s="2"/>
+      <c r="H22" s="1"/>
+      <c r="I22" s="1"/>
+      <c r="J22" s="1"/>
+      <c r="K22" s="1"/>
+      <c r="L22" s="1"/>
+      <c r="M22" s="1"/>
+      <c r="N22" s="1"/>
+      <c r="O22" s="1"/>
+      <c r="P22" s="2"/>
+      <c r="Q22" s="2"/>
+      <c r="R22" s="2"/>
+      <c r="S22" s="1"/>
+      <c r="T22"/>
+      <c r="U22" s="2"/>
+      <c r="V22" s="1"/>
+      <c r="W22" s="1"/>
+      <c r="X22" s="1"/>
+      <c r="Y22" s="1"/>
+      <c r="Z22" s="1"/>
+      <c r="AA22" s="1"/>
+    </row>
+    <row r="23" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="10"/>
+      <c r="B23" s="10"/>
+      <c r="C23" s="10"/>
+      <c r="D23" s="10"/>
+      <c r="F23" s="1"/>
+      <c r="G23" s="2"/>
+      <c r="H23" s="1"/>
+      <c r="I23" s="1"/>
+      <c r="J23" s="1"/>
+      <c r="K23" s="1"/>
+      <c r="L23" s="1"/>
+      <c r="M23" s="1"/>
+      <c r="N23" s="1"/>
+      <c r="O23" s="1"/>
+      <c r="P23" s="2"/>
+      <c r="Q23" s="2"/>
+      <c r="R23" s="2"/>
+      <c r="S23" s="1"/>
+      <c r="T23"/>
+      <c r="U23" s="2"/>
+      <c r="V23" s="1"/>
+      <c r="W23" s="1"/>
+      <c r="X23" s="1"/>
+      <c r="Y23" s="1"/>
+      <c r="Z23" s="1"/>
+      <c r="AA23" s="1"/>
+    </row>
+    <row r="24" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="10"/>
+      <c r="B24" s="10"/>
+      <c r="C24" s="10"/>
+      <c r="D24" s="10"/>
+      <c r="F24" s="1"/>
+      <c r="G24" s="2"/>
+      <c r="H24" s="1"/>
+      <c r="I24" s="1"/>
+      <c r="J24" s="1"/>
+      <c r="K24" s="1"/>
+      <c r="L24" s="1"/>
+      <c r="M24" s="1"/>
+      <c r="N24" s="1"/>
+      <c r="O24" s="1"/>
+      <c r="P24" s="2"/>
+      <c r="Q24" s="2"/>
+      <c r="R24" s="2"/>
+      <c r="S24" s="1"/>
+      <c r="T24"/>
+      <c r="U24" s="2"/>
+      <c r="V24" s="1"/>
+      <c r="W24" s="1"/>
+      <c r="X24" s="1"/>
+      <c r="Y24" s="1"/>
+      <c r="Z24" s="1"/>
+      <c r="AA24" s="1"/>
+    </row>
+    <row r="25" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="10"/>
+      <c r="B25" s="10"/>
+      <c r="C25" s="10"/>
+      <c r="D25" s="10"/>
+      <c r="F25" s="1"/>
+      <c r="G25" s="2"/>
+      <c r="H25" s="1"/>
+      <c r="I25" s="1"/>
+      <c r="J25" s="1"/>
+      <c r="K25" s="1"/>
+      <c r="L25" s="1"/>
+      <c r="M25" s="1"/>
+      <c r="N25" s="1"/>
+      <c r="O25" s="1"/>
+      <c r="P25" s="2"/>
+      <c r="Q25" s="2"/>
+      <c r="R25" s="2"/>
+      <c r="S25" s="1"/>
+      <c r="T25"/>
+      <c r="U25" s="2"/>
+      <c r="V25" s="1"/>
+      <c r="W25" s="1"/>
+      <c r="X25" s="1"/>
+      <c r="Y25" s="1"/>
+      <c r="Z25" s="1"/>
+      <c r="AA25" s="1"/>
+    </row>
+    <row r="26" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="10"/>
+      <c r="B26" s="10"/>
+      <c r="C26" s="10"/>
+      <c r="D26" s="10"/>
+      <c r="F26" s="1"/>
+      <c r="G26" s="2"/>
+      <c r="H26" s="1"/>
+      <c r="I26" s="1"/>
+      <c r="J26" s="1"/>
+      <c r="K26" s="1"/>
+      <c r="L26" s="1"/>
+      <c r="M26" s="1"/>
+      <c r="N26" s="1"/>
+      <c r="O26" s="1"/>
+      <c r="P26" s="2"/>
+      <c r="Q26" s="2"/>
+      <c r="R26" s="2"/>
+      <c r="S26" s="1"/>
+      <c r="T26"/>
+      <c r="U26" s="2"/>
+      <c r="V26" s="1"/>
+      <c r="W26" s="1"/>
+      <c r="X26" s="1"/>
+      <c r="Y26" s="1"/>
+      <c r="Z26" s="1"/>
+      <c r="AA26" s="1"/>
+    </row>
+    <row r="27" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="10"/>
+      <c r="B27" s="10"/>
+      <c r="C27" s="10"/>
+      <c r="D27" s="10"/>
+      <c r="F27" s="1"/>
+      <c r="G27" s="2"/>
+      <c r="H27" s="1"/>
+      <c r="I27" s="1"/>
+      <c r="J27" s="1"/>
+      <c r="K27" s="1"/>
+      <c r="L27" s="1"/>
+      <c r="M27" s="1"/>
+      <c r="N27" s="1"/>
+      <c r="O27" s="1"/>
+      <c r="P27" s="2"/>
+      <c r="Q27" s="2"/>
+      <c r="R27" s="2"/>
+      <c r="S27" s="1"/>
+      <c r="T27"/>
+      <c r="U27" s="2"/>
+      <c r="V27" s="1"/>
+      <c r="W27" s="1"/>
+      <c r="X27" s="1"/>
+      <c r="Y27" s="1"/>
+      <c r="Z27" s="1"/>
+      <c r="AA27" s="1"/>
+    </row>
+    <row r="28" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="10"/>
+      <c r="B28" s="10"/>
+      <c r="C28" s="10"/>
+      <c r="D28" s="10"/>
+      <c r="F28" s="1"/>
+      <c r="G28" s="2"/>
+      <c r="H28" s="1"/>
+      <c r="I28" s="1"/>
+      <c r="J28" s="1"/>
+      <c r="K28" s="1"/>
+      <c r="L28" s="1"/>
+      <c r="M28" s="1"/>
+      <c r="N28" s="1"/>
+      <c r="O28" s="1"/>
+      <c r="P28" s="2"/>
+      <c r="Q28" s="2"/>
+      <c r="R28" s="2"/>
+      <c r="S28" s="1"/>
+      <c r="T28"/>
+      <c r="U28" s="2"/>
+      <c r="V28" s="1"/>
+      <c r="W28" s="1"/>
+      <c r="X28" s="1"/>
+      <c r="Y28" s="1"/>
+      <c r="Z28" s="1"/>
+      <c r="AA28" s="1"/>
+    </row>
+    <row r="29" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="10"/>
+      <c r="B29" s="10"/>
+      <c r="C29" s="10"/>
+      <c r="D29" s="10"/>
+      <c r="F29" s="1"/>
+      <c r="G29" s="2"/>
+      <c r="H29" s="1"/>
+      <c r="I29" s="1"/>
+      <c r="J29" s="1"/>
+      <c r="K29" s="1"/>
+      <c r="L29" s="1"/>
+      <c r="M29" s="1"/>
+      <c r="N29" s="1"/>
+      <c r="O29" s="1"/>
+      <c r="P29" s="2"/>
+      <c r="Q29" s="2"/>
+      <c r="R29" s="2"/>
+      <c r="S29" s="1"/>
+      <c r="T29"/>
+      <c r="U29" s="2"/>
+      <c r="V29" s="1"/>
+      <c r="W29" s="1"/>
+      <c r="X29" s="1"/>
+      <c r="Y29" s="1"/>
+      <c r="Z29" s="1"/>
+      <c r="AA29" s="1"/>
+    </row>
+    <row r="30" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="10"/>
+      <c r="B30" s="10"/>
+      <c r="C30" s="10"/>
+      <c r="D30" s="10"/>
+      <c r="F30" s="1"/>
+      <c r="G30" s="2"/>
+      <c r="H30" s="1"/>
+      <c r="I30" s="1"/>
+      <c r="J30" s="1"/>
+      <c r="K30" s="1"/>
+      <c r="L30" s="1"/>
+      <c r="M30" s="1"/>
+      <c r="N30" s="1"/>
+      <c r="O30" s="1"/>
+      <c r="P30" s="2"/>
+      <c r="Q30" s="2"/>
+      <c r="R30" s="2"/>
+      <c r="S30" s="1"/>
+      <c r="T30"/>
+      <c r="U30" s="2"/>
+      <c r="V30" s="1"/>
+      <c r="W30" s="1"/>
+      <c r="X30" s="1"/>
+      <c r="Y30" s="1"/>
+      <c r="Z30" s="1"/>
+      <c r="AA30" s="1"/>
+    </row>
+    <row r="31" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="10"/>
+      <c r="B31" s="10"/>
+      <c r="C31" s="10"/>
+      <c r="D31" s="10"/>
+      <c r="F31" s="1"/>
+      <c r="G31" s="2"/>
+      <c r="H31" s="1"/>
+      <c r="I31" s="1"/>
+      <c r="J31" s="1"/>
+      <c r="K31" s="1"/>
+      <c r="L31" s="1"/>
+      <c r="M31" s="1"/>
+      <c r="N31" s="1"/>
+      <c r="O31" s="1"/>
+      <c r="P31" s="2"/>
+      <c r="Q31" s="2"/>
+      <c r="R31" s="2"/>
+      <c r="S31" s="1"/>
+      <c r="T31"/>
+      <c r="U31" s="2"/>
+      <c r="V31" s="1"/>
+      <c r="W31" s="1"/>
+      <c r="X31" s="1"/>
+      <c r="Y31" s="1"/>
+      <c r="Z31" s="1"/>
+      <c r="AA31" s="1"/>
+    </row>
+    <row r="32" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="10"/>
+      <c r="B32" s="10"/>
+      <c r="C32" s="10"/>
+      <c r="D32" s="10"/>
+      <c r="F32" s="1"/>
+      <c r="G32" s="2"/>
+      <c r="H32" s="1"/>
+      <c r="I32" s="1"/>
+      <c r="J32" s="1"/>
+      <c r="K32" s="1"/>
+      <c r="L32" s="1"/>
+      <c r="M32" s="1"/>
+      <c r="N32" s="1"/>
+      <c r="O32" s="1"/>
+      <c r="P32" s="2"/>
+      <c r="Q32" s="2"/>
+      <c r="R32" s="2"/>
+      <c r="S32" s="1"/>
+      <c r="T32"/>
+      <c r="U32" s="2"/>
+      <c r="V32" s="1"/>
+      <c r="W32" s="1"/>
+      <c r="X32" s="1"/>
+      <c r="Y32" s="1"/>
+      <c r="Z32" s="1"/>
+      <c r="AA32" s="1"/>
+    </row>
+    <row r="33" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="10"/>
+      <c r="B33" s="10"/>
+      <c r="C33" s="10"/>
+      <c r="D33" s="10"/>
+      <c r="F33" s="1"/>
+      <c r="G33" s="2"/>
+      <c r="H33" s="1"/>
+      <c r="I33" s="1"/>
+      <c r="J33" s="1"/>
+      <c r="K33" s="1"/>
+      <c r="L33" s="1"/>
+      <c r="M33" s="1"/>
+      <c r="N33" s="1"/>
+      <c r="O33" s="1"/>
+      <c r="P33" s="2"/>
+      <c r="Q33" s="2"/>
+      <c r="R33" s="2"/>
+      <c r="S33" s="1"/>
+      <c r="T33"/>
+      <c r="U33" s="2"/>
+      <c r="V33" s="1"/>
+      <c r="W33" s="1"/>
+      <c r="X33" s="1"/>
+      <c r="Y33" s="1"/>
+      <c r="Z33" s="1"/>
+      <c r="AA33" s="1"/>
+    </row>
+    <row r="34" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="10"/>
+      <c r="B34" s="10"/>
+      <c r="C34" s="10"/>
+      <c r="D34" s="10"/>
+      <c r="F34" s="1"/>
+      <c r="G34" s="2"/>
+      <c r="H34" s="1"/>
+      <c r="I34" s="1"/>
+      <c r="J34" s="1"/>
+      <c r="K34" s="1"/>
+      <c r="L34" s="1"/>
+      <c r="M34" s="1"/>
+      <c r="N34" s="1"/>
+      <c r="O34" s="1"/>
+      <c r="P34" s="2"/>
+      <c r="Q34" s="2"/>
+      <c r="R34" s="2"/>
+      <c r="S34" s="1"/>
+      <c r="T34"/>
+      <c r="U34" s="2"/>
+      <c r="V34" s="1"/>
+      <c r="W34" s="1"/>
+      <c r="X34" s="1"/>
+      <c r="Y34" s="1"/>
+      <c r="Z34" s="1"/>
+      <c r="AA34" s="1"/>
+    </row>
+    <row r="35" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="10"/>
+      <c r="B35" s="10"/>
+      <c r="C35" s="10"/>
+      <c r="D35" s="10"/>
+      <c r="F35" s="1"/>
+      <c r="G35" s="2"/>
+      <c r="H35" s="1"/>
+      <c r="I35" s="1"/>
+      <c r="J35" s="1"/>
+      <c r="K35" s="1"/>
+      <c r="L35" s="1"/>
+      <c r="M35" s="1"/>
+      <c r="N35" s="1"/>
+      <c r="O35" s="1"/>
+      <c r="P35" s="2"/>
+      <c r="Q35" s="2"/>
+      <c r="R35" s="2"/>
+      <c r="S35" s="1"/>
+      <c r="T35"/>
+      <c r="U35" s="2"/>
+      <c r="V35" s="1"/>
+      <c r="W35" s="1"/>
+      <c r="X35" s="1"/>
+      <c r="Y35" s="1"/>
+      <c r="Z35" s="1"/>
+      <c r="AA35" s="1"/>
+    </row>
+    <row r="36" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="10"/>
+      <c r="B36" s="10"/>
+      <c r="C36" s="10"/>
+      <c r="D36" s="10"/>
+      <c r="F36" s="1"/>
+      <c r="G36" s="2"/>
+      <c r="H36" s="1"/>
+      <c r="I36" s="1"/>
+      <c r="J36" s="1"/>
+      <c r="K36" s="1"/>
+      <c r="L36" s="1"/>
+      <c r="M36" s="1"/>
+      <c r="N36" s="1"/>
+      <c r="O36" s="1"/>
+      <c r="P36" s="2"/>
+      <c r="Q36" s="2"/>
+      <c r="R36" s="2"/>
+      <c r="S36" s="1"/>
+      <c r="T36"/>
+      <c r="U36" s="2"/>
+      <c r="V36" s="1"/>
+      <c r="W36" s="1"/>
+      <c r="X36" s="1"/>
+      <c r="Y36" s="1"/>
+      <c r="Z36" s="1"/>
+      <c r="AA36" s="1"/>
+    </row>
+    <row r="37" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="10"/>
+      <c r="B37" s="10"/>
+      <c r="C37" s="10"/>
+      <c r="D37" s="10"/>
+      <c r="F37" s="1"/>
+      <c r="G37" s="2"/>
+      <c r="H37" s="1"/>
+      <c r="I37" s="1"/>
+      <c r="J37" s="1"/>
+      <c r="K37" s="1"/>
+      <c r="L37" s="1"/>
+      <c r="M37" s="1"/>
+      <c r="N37" s="1"/>
+      <c r="O37" s="1"/>
+      <c r="P37" s="2"/>
+      <c r="Q37" s="2"/>
+      <c r="R37" s="2"/>
+      <c r="S37" s="1"/>
+      <c r="T37"/>
+      <c r="U37" s="2"/>
+      <c r="V37" s="1"/>
+      <c r="W37" s="1"/>
+      <c r="X37" s="1"/>
+      <c r="Y37" s="1"/>
+      <c r="Z37" s="1"/>
+      <c r="AA37" s="1"/>
+    </row>
+    <row r="38" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="10"/>
+      <c r="B38" s="10"/>
+      <c r="C38" s="10"/>
+      <c r="D38" s="10"/>
+      <c r="F38" s="1"/>
+      <c r="G38" s="2"/>
+      <c r="H38" s="1"/>
+      <c r="I38" s="1"/>
+      <c r="J38" s="1"/>
+      <c r="K38" s="1"/>
+      <c r="L38" s="1"/>
+      <c r="M38" s="1"/>
+      <c r="N38" s="1"/>
+      <c r="O38" s="1"/>
+      <c r="P38" s="2"/>
+      <c r="Q38" s="2"/>
+      <c r="R38" s="2"/>
+      <c r="S38" s="1"/>
+      <c r="T38"/>
+      <c r="U38" s="2"/>
+      <c r="V38" s="1"/>
+      <c r="W38" s="1"/>
+      <c r="X38" s="1"/>
+      <c r="Y38" s="1"/>
+      <c r="Z38" s="1"/>
+      <c r="AA38" s="1"/>
+    </row>
+    <row r="39" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="10"/>
+      <c r="B39" s="10"/>
+      <c r="C39" s="10"/>
+      <c r="D39" s="10"/>
+      <c r="F39" s="1"/>
+      <c r="G39" s="2"/>
+      <c r="H39" s="1"/>
+      <c r="I39" s="1"/>
+      <c r="J39" s="1"/>
+      <c r="K39" s="1"/>
+      <c r="L39" s="1"/>
+      <c r="M39" s="1"/>
+      <c r="N39" s="1"/>
+      <c r="O39" s="1"/>
+      <c r="P39" s="2"/>
+      <c r="Q39" s="2"/>
+      <c r="R39" s="2"/>
+      <c r="S39" s="1"/>
+      <c r="T39"/>
+      <c r="U39" s="2"/>
+      <c r="V39" s="1"/>
+      <c r="W39" s="1"/>
+      <c r="X39" s="1"/>
+      <c r="Y39" s="1"/>
+      <c r="Z39" s="1"/>
+      <c r="AA39" s="1"/>
+    </row>
+    <row r="40" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="10"/>
+      <c r="B40" s="10"/>
+      <c r="C40" s="10"/>
+      <c r="D40" s="10"/>
+      <c r="F40" s="1"/>
+      <c r="G40" s="2"/>
+      <c r="H40" s="1"/>
+      <c r="I40" s="1"/>
+      <c r="J40" s="1"/>
+      <c r="K40" s="1"/>
+      <c r="L40" s="1"/>
+      <c r="M40" s="1"/>
+      <c r="N40" s="1"/>
+      <c r="O40" s="1"/>
+      <c r="P40" s="2"/>
+      <c r="Q40" s="2"/>
+      <c r="R40" s="2"/>
+      <c r="S40" s="1"/>
+      <c r="T40"/>
+      <c r="U40" s="2"/>
+      <c r="V40" s="1"/>
+      <c r="W40" s="1"/>
+      <c r="X40" s="1"/>
+      <c r="Y40" s="1"/>
+      <c r="Z40" s="1"/>
+      <c r="AA40" s="1"/>
+    </row>
+    <row r="41" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="10"/>
+      <c r="B41" s="10"/>
+      <c r="C41" s="10"/>
+      <c r="D41" s="10"/>
+      <c r="F41" s="1"/>
+      <c r="G41" s="2"/>
+      <c r="H41" s="1"/>
+      <c r="I41" s="1"/>
+      <c r="J41" s="1"/>
+      <c r="K41" s="1"/>
+      <c r="L41" s="1"/>
+      <c r="M41" s="1"/>
+      <c r="N41" s="1"/>
+      <c r="O41" s="1"/>
+      <c r="P41" s="2"/>
+      <c r="Q41" s="2"/>
+      <c r="R41" s="2"/>
+      <c r="S41" s="1"/>
+      <c r="T41"/>
+      <c r="U41" s="2"/>
+      <c r="V41" s="1"/>
+      <c r="W41" s="1"/>
+      <c r="X41" s="1"/>
+      <c r="Y41" s="1"/>
+      <c r="Z41" s="1"/>
+      <c r="AA41" s="1"/>
+    </row>
+    <row r="42" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="10"/>
+      <c r="B42" s="10"/>
+      <c r="C42" s="10"/>
+      <c r="D42" s="10"/>
+      <c r="F42" s="1"/>
+      <c r="G42" s="2"/>
+      <c r="H42" s="1"/>
+      <c r="I42" s="1"/>
+      <c r="J42" s="1"/>
+      <c r="K42" s="1"/>
+      <c r="L42" s="1"/>
+      <c r="M42" s="1"/>
+      <c r="N42" s="1"/>
+      <c r="O42" s="1"/>
+      <c r="P42" s="2"/>
+      <c r="Q42" s="2"/>
+      <c r="R42" s="2"/>
+      <c r="S42" s="1"/>
+      <c r="T42"/>
+      <c r="U42" s="2"/>
+      <c r="V42" s="1"/>
+      <c r="W42" s="1"/>
+      <c r="X42" s="1"/>
+      <c r="Y42" s="1"/>
+      <c r="Z42" s="1"/>
+      <c r="AA42" s="1"/>
+    </row>
+    <row r="43" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="10"/>
+      <c r="B43" s="10"/>
+      <c r="C43" s="10"/>
+      <c r="D43" s="10"/>
+      <c r="F43" s="1"/>
+      <c r="G43" s="2"/>
+      <c r="H43" s="1"/>
+      <c r="I43" s="1"/>
+      <c r="J43" s="1"/>
+      <c r="K43" s="1"/>
+      <c r="L43" s="1"/>
+      <c r="M43" s="1"/>
+      <c r="N43" s="1"/>
+      <c r="O43" s="1"/>
+      <c r="P43" s="2"/>
+      <c r="Q43" s="2"/>
+      <c r="R43" s="2"/>
+      <c r="S43" s="1"/>
+      <c r="T43"/>
+      <c r="U43" s="2"/>
+      <c r="V43" s="1"/>
+      <c r="W43" s="1"/>
+      <c r="X43" s="1"/>
+      <c r="Y43" s="1"/>
+      <c r="Z43" s="1"/>
+      <c r="AA43" s="1"/>
+    </row>
+    <row r="44" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="10"/>
+      <c r="B44" s="10"/>
+      <c r="C44" s="10"/>
+      <c r="D44" s="10"/>
+      <c r="F44" s="1"/>
+      <c r="G44" s="2"/>
+      <c r="H44" s="1"/>
+      <c r="I44" s="1"/>
+      <c r="J44" s="1"/>
+      <c r="K44" s="1"/>
+      <c r="L44" s="1"/>
+      <c r="M44" s="1"/>
+      <c r="N44" s="1"/>
+      <c r="O44" s="1"/>
+      <c r="P44" s="2"/>
+      <c r="Q44" s="2"/>
+      <c r="R44" s="2"/>
+      <c r="S44" s="1"/>
+      <c r="T44"/>
+      <c r="U44" s="2"/>
+      <c r="V44" s="1"/>
+      <c r="W44" s="1"/>
+      <c r="X44" s="1"/>
+      <c r="Y44" s="1"/>
+      <c r="Z44" s="1"/>
+      <c r="AA44" s="1"/>
+    </row>
+    <row r="45" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="10"/>
+      <c r="B45" s="10"/>
+      <c r="C45" s="10"/>
+      <c r="D45" s="10"/>
+      <c r="F45" s="1"/>
+      <c r="G45" s="2"/>
+      <c r="H45" s="1"/>
+      <c r="I45" s="1"/>
+      <c r="J45" s="1"/>
+      <c r="K45" s="1"/>
+      <c r="L45" s="1"/>
+      <c r="M45" s="1"/>
+      <c r="N45" s="1"/>
+      <c r="O45" s="1"/>
+      <c r="P45" s="2"/>
+      <c r="Q45" s="2"/>
+      <c r="R45" s="2"/>
+      <c r="S45" s="1"/>
+      <c r="T45"/>
+      <c r="U45" s="2"/>
+      <c r="V45" s="1"/>
+      <c r="W45" s="1"/>
+      <c r="X45" s="1"/>
+      <c r="Y45" s="1"/>
+      <c r="Z45" s="1"/>
+      <c r="AA45" s="1"/>
+    </row>
+    <row r="46" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="10"/>
+      <c r="B46" s="10"/>
+      <c r="C46" s="10"/>
+      <c r="D46" s="10"/>
+      <c r="F46" s="1"/>
+      <c r="G46" s="2"/>
+      <c r="H46" s="1"/>
+      <c r="I46" s="1"/>
+      <c r="J46" s="1"/>
+      <c r="K46" s="1"/>
+      <c r="L46" s="1"/>
+      <c r="M46" s="1"/>
+      <c r="N46" s="1"/>
+      <c r="O46" s="1"/>
+      <c r="P46" s="2"/>
+      <c r="Q46" s="2"/>
+      <c r="R46" s="2"/>
+      <c r="S46" s="1"/>
+      <c r="T46"/>
+      <c r="U46" s="2"/>
+      <c r="V46" s="1"/>
+      <c r="W46" s="1"/>
+      <c r="X46" s="1"/>
+      <c r="Y46" s="1"/>
+      <c r="Z46" s="1"/>
+      <c r="AA46" s="1"/>
+    </row>
+    <row r="47" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="10"/>
+      <c r="B47" s="10"/>
+      <c r="C47" s="10"/>
+      <c r="D47" s="10"/>
+      <c r="F47" s="1"/>
+      <c r="G47" s="2"/>
+      <c r="H47" s="1"/>
+      <c r="I47" s="1"/>
+      <c r="J47" s="1"/>
+      <c r="K47" s="1"/>
+      <c r="L47" s="1"/>
+      <c r="M47" s="1"/>
+      <c r="N47" s="1"/>
+      <c r="O47" s="1"/>
+      <c r="P47" s="2"/>
+      <c r="Q47" s="2"/>
+      <c r="R47" s="2"/>
+      <c r="S47" s="1"/>
+      <c r="T47"/>
+      <c r="U47" s="2"/>
+      <c r="V47" s="1"/>
+      <c r="W47" s="1"/>
+      <c r="X47" s="1"/>
+      <c r="Y47" s="1"/>
+      <c r="Z47" s="1"/>
+      <c r="AA47" s="1"/>
+    </row>
+    <row r="48" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="10"/>
+      <c r="B48" s="10"/>
+      <c r="C48" s="10"/>
+      <c r="D48" s="10"/>
+      <c r="F48" s="1"/>
+      <c r="G48" s="2"/>
+      <c r="H48" s="1"/>
+      <c r="I48" s="1"/>
+      <c r="J48" s="1"/>
+      <c r="K48" s="1"/>
+      <c r="L48" s="1"/>
+      <c r="M48" s="1"/>
+      <c r="N48" s="1"/>
+      <c r="O48" s="1"/>
+      <c r="P48" s="2"/>
+      <c r="Q48" s="2"/>
+      <c r="R48" s="2"/>
+      <c r="S48" s="1"/>
+      <c r="T48"/>
+      <c r="U48" s="2"/>
+      <c r="V48" s="1"/>
+      <c r="W48" s="1"/>
+      <c r="X48" s="1"/>
+      <c r="Y48" s="1"/>
+      <c r="Z48" s="1"/>
+      <c r="AA48" s="1"/>
+    </row>
+    <row r="49" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="10"/>
+      <c r="B49" s="10"/>
+      <c r="C49" s="10"/>
+      <c r="D49" s="10"/>
+      <c r="F49" s="1"/>
+      <c r="G49" s="2"/>
+      <c r="H49" s="1"/>
+      <c r="I49" s="1"/>
+      <c r="J49" s="1"/>
+      <c r="K49" s="1"/>
+      <c r="L49" s="1"/>
+      <c r="M49" s="1"/>
+      <c r="N49" s="1"/>
+      <c r="O49" s="1"/>
+      <c r="P49" s="2"/>
+      <c r="Q49" s="2"/>
+      <c r="R49" s="2"/>
+      <c r="S49" s="1"/>
+      <c r="T49"/>
+      <c r="U49" s="2"/>
+      <c r="V49" s="1"/>
+      <c r="W49" s="1"/>
+      <c r="X49" s="1"/>
+      <c r="Y49" s="1"/>
+      <c r="Z49" s="1"/>
+      <c r="AA49" s="1"/>
+    </row>
+    <row r="50" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="10"/>
+      <c r="B50" s="10"/>
+      <c r="C50" s="10"/>
+      <c r="D50" s="10"/>
+      <c r="F50" s="1"/>
+      <c r="G50" s="2"/>
+      <c r="H50" s="1"/>
+      <c r="I50" s="1"/>
+      <c r="J50" s="1"/>
+      <c r="K50" s="1"/>
+      <c r="L50" s="1"/>
+      <c r="M50" s="1"/>
+      <c r="N50" s="1"/>
+      <c r="O50" s="1"/>
+      <c r="P50" s="2"/>
+      <c r="Q50" s="2"/>
+      <c r="R50" s="2"/>
+      <c r="S50" s="1"/>
+      <c r="T50"/>
+      <c r="U50" s="2"/>
+      <c r="V50" s="1"/>
+      <c r="W50" s="1"/>
+      <c r="X50" s="1"/>
+      <c r="Y50" s="1"/>
+      <c r="Z50" s="1"/>
+      <c r="AA50" s="1"/>
+    </row>
+    <row r="51" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="10"/>
+      <c r="B51" s="10"/>
+      <c r="C51" s="10"/>
+      <c r="D51" s="10"/>
+      <c r="F51" s="1"/>
+      <c r="G51" s="2"/>
+      <c r="H51" s="1"/>
+      <c r="I51" s="1"/>
+      <c r="J51" s="1"/>
+      <c r="K51" s="1"/>
+      <c r="L51" s="1"/>
+      <c r="M51" s="1"/>
+      <c r="N51" s="1"/>
+      <c r="O51" s="1"/>
+      <c r="P51" s="2"/>
+      <c r="Q51" s="2"/>
+      <c r="R51" s="2"/>
+      <c r="S51" s="1"/>
+      <c r="T51"/>
+      <c r="U51" s="2"/>
+      <c r="V51" s="1"/>
+      <c r="W51" s="1"/>
+      <c r="X51" s="1"/>
+      <c r="Y51" s="1"/>
+      <c r="Z51" s="1"/>
+      <c r="AA51" s="1"/>
+    </row>
+    <row r="52" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="10"/>
+      <c r="B52" s="10"/>
+      <c r="C52" s="10"/>
+      <c r="D52" s="10"/>
+      <c r="F52" s="1"/>
+      <c r="G52" s="2"/>
+      <c r="H52" s="1"/>
+      <c r="I52" s="1"/>
+      <c r="J52" s="1"/>
+      <c r="K52" s="1"/>
+      <c r="L52" s="1"/>
+      <c r="M52" s="1"/>
+      <c r="N52" s="1"/>
+      <c r="O52" s="1"/>
+      <c r="P52" s="2"/>
+      <c r="Q52" s="2"/>
+      <c r="R52" s="2"/>
+      <c r="S52" s="1"/>
+      <c r="T52"/>
+      <c r="U52" s="2"/>
+      <c r="V52" s="1"/>
+      <c r="W52" s="1"/>
+      <c r="X52" s="1"/>
+      <c r="Y52" s="1"/>
+      <c r="Z52" s="1"/>
+      <c r="AA52" s="1"/>
+    </row>
+    <row r="53" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="10"/>
+      <c r="B53" s="10"/>
+      <c r="C53" s="10"/>
+      <c r="D53" s="10"/>
+      <c r="F53" s="1"/>
+      <c r="G53" s="2"/>
+      <c r="H53" s="1"/>
+      <c r="I53" s="1"/>
+      <c r="J53" s="1"/>
+      <c r="K53" s="1"/>
+      <c r="L53" s="1"/>
+      <c r="M53" s="1"/>
+      <c r="N53" s="1"/>
+      <c r="O53" s="1"/>
+      <c r="P53" s="2"/>
+      <c r="Q53" s="2"/>
+      <c r="R53" s="2"/>
+      <c r="S53" s="1"/>
+      <c r="T53"/>
+      <c r="U53" s="2"/>
+      <c r="V53" s="1"/>
+      <c r="W53" s="1"/>
+      <c r="X53" s="1"/>
+      <c r="Y53" s="1"/>
+      <c r="Z53" s="1"/>
+      <c r="AA53" s="1"/>
+    </row>
+    <row r="54" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="10"/>
+      <c r="B54" s="10"/>
+      <c r="C54" s="10"/>
+      <c r="D54" s="10"/>
+      <c r="F54" s="1"/>
+      <c r="G54" s="2"/>
+      <c r="H54" s="1"/>
+      <c r="I54" s="1"/>
+      <c r="J54" s="1"/>
+      <c r="K54" s="1"/>
+      <c r="L54" s="1"/>
+      <c r="M54" s="1"/>
+      <c r="N54" s="1"/>
+      <c r="O54" s="1"/>
+      <c r="P54" s="2"/>
+      <c r="Q54" s="2"/>
+      <c r="R54" s="2"/>
+      <c r="S54" s="1"/>
+      <c r="T54"/>
+      <c r="U54" s="2"/>
+      <c r="V54" s="1"/>
+      <c r="W54" s="1"/>
+      <c r="X54" s="1"/>
+      <c r="Y54" s="1"/>
+      <c r="Z54" s="1"/>
+      <c r="AA54" s="1"/>
+    </row>
+    <row r="55" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A55" s="10"/>
       <c r="B55" s="10"/>
       <c r="C55" s="10"/>
       <c r="D55" s="10"/>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="F55" s="1"/>
+      <c r="G55" s="2"/>
+      <c r="H55" s="1"/>
+      <c r="I55" s="1"/>
+      <c r="J55" s="1"/>
+      <c r="K55" s="1"/>
+      <c r="L55" s="1"/>
+      <c r="M55" s="1"/>
+      <c r="N55" s="1"/>
+      <c r="O55" s="1"/>
+      <c r="P55" s="2"/>
+      <c r="Q55" s="2"/>
+      <c r="R55" s="2"/>
+      <c r="S55" s="1"/>
+      <c r="T55"/>
+      <c r="U55" s="2"/>
+      <c r="V55" s="1"/>
+      <c r="W55" s="1"/>
+      <c r="X55" s="1"/>
+      <c r="Y55" s="1"/>
+      <c r="Z55" s="1"/>
+      <c r="AA55" s="1"/>
+    </row>
+    <row r="56" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A56" s="10"/>
       <c r="B56" s="10"/>
       <c r="C56" s="10"/>
       <c r="D56" s="10"/>
-    </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="F56" s="1"/>
+      <c r="G56" s="2"/>
+      <c r="H56" s="1"/>
+      <c r="I56" s="1"/>
+      <c r="J56" s="1"/>
+      <c r="K56" s="1"/>
+      <c r="L56" s="1"/>
+      <c r="M56" s="1"/>
+      <c r="N56" s="1"/>
+      <c r="O56" s="1"/>
+      <c r="P56" s="2"/>
+      <c r="Q56" s="2"/>
+      <c r="R56" s="2"/>
+      <c r="S56" s="1"/>
+      <c r="T56"/>
+      <c r="U56" s="2"/>
+      <c r="V56" s="1"/>
+      <c r="W56" s="1"/>
+      <c r="X56" s="1"/>
+      <c r="Y56" s="1"/>
+      <c r="Z56" s="1"/>
+      <c r="AA56" s="1"/>
+    </row>
+    <row r="57" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A57" s="10"/>
       <c r="B57" s="10"/>
       <c r="C57" s="10"/>
       <c r="D57" s="10"/>
-    </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="F57" s="1"/>
+      <c r="G57" s="2"/>
+      <c r="H57" s="1"/>
+      <c r="I57" s="1"/>
+      <c r="J57" s="1"/>
+      <c r="K57" s="1"/>
+      <c r="L57" s="1"/>
+      <c r="M57" s="1"/>
+      <c r="N57" s="1"/>
+      <c r="O57" s="1"/>
+      <c r="P57" s="2"/>
+      <c r="Q57" s="2"/>
+      <c r="R57" s="2"/>
+      <c r="S57" s="1"/>
+      <c r="T57"/>
+      <c r="U57" s="2"/>
+      <c r="V57" s="1"/>
+      <c r="W57" s="1"/>
+      <c r="X57" s="1"/>
+      <c r="Y57" s="1"/>
+      <c r="Z57" s="1"/>
+      <c r="AA57" s="1"/>
+    </row>
+    <row r="58" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A58" s="10"/>
       <c r="B58" s="10"/>
       <c r="C58" s="10"/>
       <c r="D58" s="10"/>
-    </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="F58" s="1"/>
+      <c r="G58" s="2"/>
+      <c r="H58" s="1"/>
+      <c r="I58" s="1"/>
+      <c r="J58" s="1"/>
+      <c r="K58" s="1"/>
+      <c r="L58" s="1"/>
+      <c r="M58" s="1"/>
+      <c r="N58" s="1"/>
+      <c r="O58" s="1"/>
+      <c r="P58" s="2"/>
+      <c r="Q58" s="2"/>
+      <c r="R58" s="2"/>
+      <c r="S58" s="1"/>
+      <c r="T58"/>
+      <c r="U58" s="2"/>
+      <c r="V58" s="1"/>
+      <c r="W58" s="1"/>
+      <c r="X58" s="1"/>
+      <c r="Y58" s="1"/>
+      <c r="Z58" s="1"/>
+      <c r="AA58" s="1"/>
+    </row>
+    <row r="59" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A59" s="10"/>
       <c r="B59" s="10"/>
       <c r="C59" s="10"/>
       <c r="D59" s="10"/>
-    </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="F59" s="1"/>
+      <c r="G59" s="2"/>
+      <c r="H59" s="1"/>
+      <c r="I59" s="1"/>
+      <c r="J59" s="1"/>
+      <c r="K59" s="1"/>
+      <c r="L59" s="1"/>
+      <c r="M59" s="1"/>
+      <c r="N59" s="1"/>
+      <c r="O59" s="1"/>
+      <c r="P59" s="2"/>
+      <c r="Q59" s="2"/>
+      <c r="R59" s="2"/>
+      <c r="S59" s="1"/>
+      <c r="T59"/>
+      <c r="U59" s="2"/>
+      <c r="V59" s="1"/>
+      <c r="W59" s="1"/>
+      <c r="X59" s="1"/>
+      <c r="Y59" s="1"/>
+      <c r="Z59" s="1"/>
+      <c r="AA59" s="1"/>
+    </row>
+    <row r="60" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A60" s="10"/>
       <c r="B60" s="10"/>
       <c r="C60" s="10"/>
       <c r="D60" s="10"/>
-    </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="F60" s="1"/>
+      <c r="G60" s="2"/>
+      <c r="H60" s="1"/>
+      <c r="I60" s="1"/>
+      <c r="J60" s="1"/>
+      <c r="K60" s="1"/>
+      <c r="L60" s="1"/>
+      <c r="M60" s="1"/>
+      <c r="N60" s="1"/>
+      <c r="O60" s="1"/>
+      <c r="P60" s="2"/>
+      <c r="Q60" s="2"/>
+      <c r="R60" s="2"/>
+      <c r="S60" s="1"/>
+      <c r="T60"/>
+      <c r="U60" s="2"/>
+      <c r="V60" s="1"/>
+      <c r="W60" s="1"/>
+      <c r="X60" s="1"/>
+      <c r="Y60" s="1"/>
+      <c r="Z60" s="1"/>
+      <c r="AA60" s="1"/>
+    </row>
+    <row r="61" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A61" s="10"/>
       <c r="B61" s="10"/>
       <c r="C61" s="10"/>
       <c r="D61" s="10"/>
-    </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="F61" s="1"/>
+      <c r="G61" s="2"/>
+      <c r="H61" s="1"/>
+      <c r="I61" s="1"/>
+      <c r="J61" s="1"/>
+      <c r="K61" s="1"/>
+      <c r="L61" s="1"/>
+      <c r="M61" s="1"/>
+      <c r="N61" s="1"/>
+      <c r="O61" s="1"/>
+      <c r="P61" s="2"/>
+      <c r="Q61" s="2"/>
+      <c r="R61" s="2"/>
+      <c r="S61" s="1"/>
+      <c r="T61"/>
+      <c r="U61" s="2"/>
+      <c r="V61" s="1"/>
+      <c r="W61" s="1"/>
+      <c r="X61" s="1"/>
+      <c r="Y61" s="1"/>
+      <c r="Z61" s="1"/>
+      <c r="AA61" s="1"/>
+    </row>
+    <row r="62" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A62" s="10"/>
       <c r="B62" s="10"/>
       <c r="C62" s="10"/>
       <c r="D62" s="10"/>
-    </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="F62" s="1"/>
+      <c r="G62" s="2"/>
+      <c r="H62" s="1"/>
+      <c r="I62" s="1"/>
+      <c r="J62" s="1"/>
+      <c r="K62" s="1"/>
+      <c r="L62" s="1"/>
+      <c r="M62" s="1"/>
+      <c r="N62" s="1"/>
+      <c r="O62" s="1"/>
+      <c r="P62" s="2"/>
+      <c r="Q62" s="2"/>
+      <c r="R62" s="2"/>
+      <c r="S62" s="1"/>
+      <c r="T62"/>
+      <c r="U62" s="2"/>
+      <c r="V62" s="1"/>
+      <c r="W62" s="1"/>
+      <c r="X62" s="1"/>
+      <c r="Y62" s="1"/>
+      <c r="Z62" s="1"/>
+      <c r="AA62" s="1"/>
+    </row>
+    <row r="63" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A63" s="10"/>
       <c r="B63" s="10"/>
       <c r="C63" s="10"/>
       <c r="D63" s="10"/>
-    </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="F63" s="1"/>
+      <c r="G63" s="2"/>
+      <c r="H63" s="1"/>
+      <c r="I63" s="1"/>
+      <c r="J63" s="1"/>
+      <c r="K63" s="1"/>
+      <c r="L63" s="1"/>
+      <c r="M63" s="1"/>
+      <c r="N63" s="1"/>
+      <c r="O63" s="1"/>
+      <c r="P63" s="2"/>
+      <c r="Q63" s="2"/>
+      <c r="R63" s="2"/>
+      <c r="S63" s="1"/>
+      <c r="T63"/>
+      <c r="U63" s="2"/>
+      <c r="V63" s="1"/>
+      <c r="W63" s="1"/>
+      <c r="X63" s="1"/>
+      <c r="Y63" s="1"/>
+      <c r="Z63" s="1"/>
+      <c r="AA63" s="1"/>
+    </row>
+    <row r="64" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A64" s="10"/>
       <c r="B64" s="10"/>
       <c r="C64" s="10"/>
       <c r="D64" s="10"/>
-    </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="F64" s="1"/>
+      <c r="G64" s="2"/>
+      <c r="H64" s="1"/>
+      <c r="I64" s="1"/>
+      <c r="J64" s="1"/>
+      <c r="K64" s="1"/>
+      <c r="L64" s="1"/>
+      <c r="M64" s="1"/>
+      <c r="N64" s="1"/>
+      <c r="O64" s="1"/>
+      <c r="P64" s="2"/>
+      <c r="Q64" s="2"/>
+      <c r="R64" s="2"/>
+      <c r="S64" s="1"/>
+      <c r="T64"/>
+      <c r="U64" s="2"/>
+      <c r="V64" s="1"/>
+      <c r="W64" s="1"/>
+      <c r="X64" s="1"/>
+      <c r="Y64" s="1"/>
+      <c r="Z64" s="1"/>
+      <c r="AA64" s="1"/>
+    </row>
+    <row r="65" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A65" s="10"/>
       <c r="B65" s="10"/>
       <c r="C65" s="10"/>
       <c r="D65" s="10"/>
-    </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="F65" s="1"/>
+      <c r="G65" s="2"/>
+      <c r="H65" s="1"/>
+      <c r="I65" s="1"/>
+      <c r="J65" s="1"/>
+      <c r="K65" s="1"/>
+      <c r="L65" s="1"/>
+      <c r="M65" s="1"/>
+      <c r="N65" s="1"/>
+      <c r="O65" s="1"/>
+      <c r="P65" s="2"/>
+      <c r="Q65" s="2"/>
+      <c r="R65" s="2"/>
+      <c r="S65" s="1"/>
+      <c r="T65"/>
+      <c r="U65" s="2"/>
+      <c r="V65" s="1"/>
+      <c r="W65" s="1"/>
+      <c r="X65" s="1"/>
+      <c r="Y65" s="1"/>
+      <c r="Z65" s="1"/>
+      <c r="AA65" s="1"/>
+    </row>
+    <row r="66" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A66" s="10"/>
       <c r="B66" s="10"/>
       <c r="C66" s="10"/>
       <c r="D66" s="10"/>
-    </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="F66" s="1"/>
+      <c r="G66" s="2"/>
+      <c r="H66" s="1"/>
+      <c r="I66" s="1"/>
+      <c r="J66" s="1"/>
+      <c r="K66" s="1"/>
+      <c r="L66" s="1"/>
+      <c r="M66" s="1"/>
+      <c r="N66" s="1"/>
+      <c r="O66" s="1"/>
+      <c r="P66" s="2"/>
+      <c r="Q66" s="2"/>
+      <c r="R66" s="2"/>
+      <c r="S66" s="1"/>
+      <c r="T66"/>
+      <c r="U66" s="2"/>
+      <c r="V66" s="1"/>
+      <c r="W66" s="1"/>
+      <c r="X66" s="1"/>
+      <c r="Y66" s="1"/>
+      <c r="Z66" s="1"/>
+      <c r="AA66" s="1"/>
+    </row>
+    <row r="67" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A67" s="10"/>
       <c r="B67" s="10"/>
       <c r="C67" s="10"/>
       <c r="D67" s="10"/>
-    </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="F67" s="1"/>
+      <c r="G67" s="2"/>
+      <c r="H67" s="1"/>
+      <c r="I67" s="1"/>
+      <c r="J67" s="1"/>
+      <c r="K67" s="1"/>
+      <c r="L67" s="1"/>
+      <c r="M67" s="1"/>
+      <c r="N67" s="1"/>
+      <c r="O67" s="1"/>
+      <c r="P67" s="2"/>
+      <c r="Q67" s="2"/>
+      <c r="R67" s="2"/>
+      <c r="S67" s="1"/>
+      <c r="T67"/>
+      <c r="U67" s="2"/>
+      <c r="V67" s="1"/>
+      <c r="W67" s="1"/>
+      <c r="X67" s="1"/>
+      <c r="Y67" s="1"/>
+      <c r="Z67" s="1"/>
+      <c r="AA67" s="1"/>
+    </row>
+    <row r="68" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A68" s="10"/>
       <c r="B68" s="10"/>
       <c r="C68" s="10"/>
       <c r="D68" s="10"/>
-    </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="F68" s="1"/>
+      <c r="G68" s="2"/>
+      <c r="H68" s="1"/>
+      <c r="I68" s="1"/>
+      <c r="J68" s="1"/>
+      <c r="K68" s="1"/>
+      <c r="L68" s="1"/>
+      <c r="M68" s="1"/>
+      <c r="N68" s="1"/>
+      <c r="O68" s="1"/>
+      <c r="P68" s="2"/>
+      <c r="Q68" s="2"/>
+      <c r="R68" s="2"/>
+      <c r="S68" s="1"/>
+      <c r="T68"/>
+      <c r="U68" s="2"/>
+      <c r="V68" s="1"/>
+      <c r="W68" s="1"/>
+      <c r="X68" s="1"/>
+      <c r="Y68" s="1"/>
+      <c r="Z68" s="1"/>
+      <c r="AA68" s="1"/>
+    </row>
+    <row r="69" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A69" s="10"/>
       <c r="B69" s="10"/>
       <c r="C69" s="10"/>
       <c r="D69" s="10"/>
-    </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="F69" s="1"/>
+      <c r="G69" s="2"/>
+      <c r="H69" s="1"/>
+      <c r="I69" s="1"/>
+      <c r="J69" s="1"/>
+      <c r="K69" s="1"/>
+      <c r="L69" s="1"/>
+      <c r="M69" s="1"/>
+      <c r="N69" s="1"/>
+      <c r="O69" s="1"/>
+      <c r="P69" s="2"/>
+      <c r="Q69" s="2"/>
+      <c r="R69" s="2"/>
+      <c r="S69" s="1"/>
+      <c r="T69"/>
+      <c r="U69" s="2"/>
+      <c r="V69" s="1"/>
+      <c r="W69" s="1"/>
+      <c r="X69" s="1"/>
+      <c r="Y69" s="1"/>
+      <c r="Z69" s="1"/>
+      <c r="AA69" s="1"/>
+    </row>
+    <row r="70" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A70" s="10"/>
       <c r="B70" s="10"/>
       <c r="C70" s="10"/>
       <c r="D70" s="10"/>
-    </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="F70" s="1"/>
+      <c r="G70" s="2"/>
+      <c r="H70" s="1"/>
+      <c r="I70" s="1"/>
+      <c r="J70" s="1"/>
+      <c r="K70" s="1"/>
+      <c r="L70" s="1"/>
+      <c r="M70" s="1"/>
+      <c r="N70" s="1"/>
+      <c r="O70" s="1"/>
+      <c r="P70" s="2"/>
+      <c r="Q70" s="2"/>
+      <c r="R70" s="2"/>
+      <c r="S70" s="1"/>
+      <c r="T70"/>
+      <c r="U70" s="2"/>
+      <c r="V70" s="1"/>
+      <c r="W70" s="1"/>
+      <c r="X70" s="1"/>
+      <c r="Y70" s="1"/>
+      <c r="Z70" s="1"/>
+      <c r="AA70" s="1"/>
+    </row>
+    <row r="71" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A71" s="10"/>
       <c r="B71" s="10"/>
       <c r="C71" s="10"/>
       <c r="D71" s="10"/>
-    </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="F71" s="1"/>
+      <c r="G71" s="2"/>
+      <c r="H71" s="1"/>
+      <c r="I71" s="1"/>
+      <c r="J71" s="1"/>
+      <c r="K71" s="1"/>
+      <c r="L71" s="1"/>
+      <c r="M71" s="1"/>
+      <c r="N71" s="1"/>
+      <c r="O71" s="1"/>
+      <c r="P71" s="2"/>
+      <c r="Q71" s="2"/>
+      <c r="R71" s="2"/>
+      <c r="S71" s="1"/>
+      <c r="T71"/>
+      <c r="U71" s="2"/>
+      <c r="V71" s="1"/>
+      <c r="W71" s="1"/>
+      <c r="X71" s="1"/>
+      <c r="Y71" s="1"/>
+      <c r="Z71" s="1"/>
+      <c r="AA71" s="1"/>
+    </row>
+    <row r="72" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A72" s="10"/>
       <c r="B72" s="10"/>
       <c r="C72" s="10"/>
       <c r="D72" s="10"/>
-    </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="F72" s="1"/>
+      <c r="G72" s="2"/>
+      <c r="H72" s="1"/>
+      <c r="I72" s="1"/>
+      <c r="J72" s="1"/>
+      <c r="K72" s="1"/>
+      <c r="L72" s="1"/>
+      <c r="M72" s="1"/>
+      <c r="N72" s="1"/>
+      <c r="O72" s="1"/>
+      <c r="P72" s="2"/>
+      <c r="Q72" s="2"/>
+      <c r="R72" s="2"/>
+      <c r="S72" s="1"/>
+      <c r="T72"/>
+      <c r="U72" s="2"/>
+      <c r="V72" s="1"/>
+      <c r="W72" s="1"/>
+      <c r="X72" s="1"/>
+      <c r="Y72" s="1"/>
+      <c r="Z72" s="1"/>
+      <c r="AA72" s="1"/>
+    </row>
+    <row r="73" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A73" s="10"/>
       <c r="B73" s="10"/>
       <c r="C73" s="10"/>
       <c r="D73" s="10"/>
-    </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="F73" s="1"/>
+      <c r="G73" s="2"/>
+      <c r="H73" s="1"/>
+      <c r="I73" s="1"/>
+      <c r="J73" s="1"/>
+      <c r="K73" s="1"/>
+      <c r="L73" s="1"/>
+      <c r="M73" s="1"/>
+      <c r="N73" s="1"/>
+      <c r="O73" s="1"/>
+      <c r="P73" s="2"/>
+      <c r="Q73" s="2"/>
+      <c r="R73" s="2"/>
+      <c r="S73" s="1"/>
+      <c r="T73"/>
+      <c r="U73" s="2"/>
+      <c r="V73" s="1"/>
+      <c r="W73" s="1"/>
+      <c r="X73" s="1"/>
+      <c r="Y73" s="1"/>
+      <c r="Z73" s="1"/>
+      <c r="AA73" s="1"/>
+    </row>
+    <row r="74" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A74" s="10"/>
       <c r="B74" s="10"/>
       <c r="C74" s="10"/>
       <c r="D74" s="10"/>
-    </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="F74" s="1"/>
+      <c r="G74" s="2"/>
+      <c r="H74" s="1"/>
+      <c r="I74" s="1"/>
+      <c r="J74" s="1"/>
+      <c r="K74" s="1"/>
+      <c r="L74" s="1"/>
+      <c r="M74" s="1"/>
+      <c r="N74" s="1"/>
+      <c r="O74" s="1"/>
+      <c r="P74" s="2"/>
+      <c r="Q74" s="2"/>
+      <c r="R74" s="2"/>
+      <c r="S74" s="1"/>
+      <c r="T74"/>
+      <c r="U74" s="2"/>
+      <c r="V74" s="1"/>
+      <c r="W74" s="1"/>
+      <c r="X74" s="1"/>
+      <c r="Y74" s="1"/>
+      <c r="Z74" s="1"/>
+      <c r="AA74" s="1"/>
+    </row>
+    <row r="75" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A75" s="10"/>
       <c r="B75" s="10"/>
       <c r="C75" s="10"/>
       <c r="D75" s="10"/>
-    </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A76" s="10"/>
-      <c r="B76" s="10"/>
-      <c r="C76" s="10"/>
-      <c r="D76" s="10"/>
-    </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A77" s="10"/>
-      <c r="B77" s="10"/>
-      <c r="C77" s="10"/>
-      <c r="D77" s="10"/>
-    </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A78" s="10"/>
-      <c r="B78" s="10"/>
-      <c r="C78" s="10"/>
-      <c r="D78" s="10"/>
-    </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A79" s="10"/>
-      <c r="B79" s="10"/>
-      <c r="C79" s="10"/>
-      <c r="D79" s="10"/>
-    </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A80" s="10"/>
-      <c r="B80" s="10"/>
-      <c r="C80" s="10"/>
-      <c r="D80" s="10"/>
-    </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A81" s="10"/>
-      <c r="B81" s="10"/>
-      <c r="C81" s="10"/>
-      <c r="D81" s="10"/>
-    </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A82" s="10"/>
-      <c r="B82" s="10"/>
-      <c r="C82" s="10"/>
-      <c r="D82" s="10"/>
-    </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A83" s="10"/>
-      <c r="B83" s="10"/>
-      <c r="C83" s="10"/>
-      <c r="D83" s="10"/>
-    </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A84" s="10"/>
-      <c r="B84" s="10"/>
-      <c r="C84" s="10"/>
-      <c r="D84" s="10"/>
-    </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A85" s="10"/>
-      <c r="B85" s="10"/>
-      <c r="C85" s="10"/>
-      <c r="D85" s="10"/>
-    </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A86" s="10"/>
-      <c r="B86" s="10"/>
-      <c r="C86" s="10"/>
-      <c r="D86" s="10"/>
-    </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A87" s="10"/>
-      <c r="B87" s="10"/>
-      <c r="C87" s="10"/>
-      <c r="D87" s="10"/>
-    </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A88" s="10"/>
-      <c r="B88" s="10"/>
-      <c r="C88" s="10"/>
-      <c r="D88" s="10"/>
-    </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A89" s="10"/>
-      <c r="B89" s="10"/>
-      <c r="C89" s="10"/>
-      <c r="D89" s="10"/>
-    </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A90" s="10"/>
-      <c r="B90" s="10"/>
-      <c r="C90" s="10"/>
-      <c r="D90" s="10"/>
-    </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A91" s="10"/>
-      <c r="B91" s="10"/>
-      <c r="C91" s="10"/>
-      <c r="D91" s="10"/>
-    </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A92" s="10"/>
-      <c r="B92" s="10"/>
-      <c r="C92" s="10"/>
-      <c r="D92" s="10"/>
-    </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A93" s="10"/>
-      <c r="B93" s="10"/>
-      <c r="C93" s="10"/>
-      <c r="D93" s="10"/>
-    </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A94" s="10"/>
-      <c r="B94" s="10"/>
-      <c r="C94" s="10"/>
-      <c r="D94" s="10"/>
-    </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A95" s="10"/>
-      <c r="B95" s="10"/>
-      <c r="C95" s="10"/>
-      <c r="D95" s="10"/>
-    </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A96" s="10"/>
-      <c r="B96" s="10"/>
-      <c r="C96" s="10"/>
-      <c r="D96" s="10"/>
-    </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A97" s="10"/>
-      <c r="B97" s="10"/>
-      <c r="C97" s="10"/>
-      <c r="D97" s="10"/>
-    </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A98" s="10"/>
-      <c r="B98" s="10"/>
-      <c r="C98" s="10"/>
-      <c r="D98" s="10"/>
-    </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A99" s="10"/>
-      <c r="B99" s="10"/>
-      <c r="C99" s="10"/>
-      <c r="D99" s="10"/>
-    </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A100" s="10"/>
-      <c r="B100" s="10"/>
-      <c r="C100" s="10"/>
-      <c r="D100" s="10"/>
-    </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A101" s="10"/>
-      <c r="B101" s="10"/>
-      <c r="C101" s="10"/>
-      <c r="D101" s="10"/>
-    </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A102" s="10"/>
-      <c r="B102" s="10"/>
-      <c r="C102" s="10"/>
-      <c r="D102" s="10"/>
-    </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A103" s="10"/>
-      <c r="B103" s="10"/>
-      <c r="C103" s="10"/>
-      <c r="D103" s="10"/>
-    </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A104" s="10"/>
-      <c r="B104" s="10"/>
-      <c r="C104" s="10"/>
-      <c r="D104" s="10"/>
-    </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A105" s="10"/>
-      <c r="B105" s="10"/>
-      <c r="C105" s="10"/>
-      <c r="D105" s="10"/>
-    </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A106" s="10"/>
-      <c r="B106" s="10"/>
-      <c r="C106" s="10"/>
-      <c r="D106" s="10"/>
-    </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A107" s="10"/>
-      <c r="B107" s="10"/>
-      <c r="C107" s="10"/>
-      <c r="D107" s="10"/>
-    </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A108" s="10"/>
-      <c r="B108" s="10"/>
-      <c r="C108" s="10"/>
-      <c r="D108" s="10"/>
+      <c r="F75" s="1"/>
+      <c r="G75" s="2"/>
+      <c r="H75" s="1"/>
+      <c r="I75" s="1"/>
+      <c r="J75" s="1"/>
+      <c r="K75" s="1"/>
+      <c r="L75" s="1"/>
+      <c r="M75" s="1"/>
+      <c r="N75" s="1"/>
+      <c r="O75" s="1"/>
+      <c r="P75" s="2"/>
+      <c r="Q75" s="2"/>
+      <c r="R75" s="2"/>
+      <c r="S75" s="1"/>
+      <c r="T75"/>
+      <c r="U75" s="2"/>
+      <c r="V75" s="1"/>
+      <c r="W75" s="1"/>
+      <c r="X75" s="1"/>
+      <c r="Y75" s="1"/>
+      <c r="Z75" s="1"/>
+      <c r="AA75" s="1"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="17" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="10" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
   <drawing r:id="rId2"/>

--- a/4 четверть_19_JavaScript_vite.xlsx
+++ b/4 четверть_19_JavaScript_vite.xlsx
@@ -8,13 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AlexServHW\Desktop\GB_Developer_Workbook\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{251CF88E-FBC9-4741-AB0C-20012C812005}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E0D2B5D-19E2-4D58-81D3-58322A654FFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="vite" sheetId="15" r:id="rId1"/>
-    <sheet name="env" sheetId="16" r:id="rId2"/>
+    <sheet name="Environment variables" sheetId="16" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="108">
   <si>
     <t>vite</t>
   </si>
@@ -705,21 +705,6 @@
   </si>
   <si>
     <t>plugins/env.js</t>
-  </si>
-  <si>
-    <t>const EnvPlugin = {
-  install(Vue) {
-    Vue.prototype.$env = {
-      isLocalProxy: import.meta.env.VITE_LOCALPROXY,
-      isElectronProxy: import.meta.env.VITE_ELECTRON_PROXY,
-      pathToBuild: import.meta.env.VITE_PAT_TO_BUILD,
-      apiProxy: import.meta.env.VITE_API_PROXY,
-      socketProxy: import.meta.env.VITE_SOCKET_PROXY,
-      fileLoaderPath: import.meta.env.VITE_FILE_LOAD,
-    }
-  }
-}
-export default EnvPlugin</t>
   </si>
   <si>
     <t>package.json</t>
@@ -1008,6 +993,46 @@
   </si>
   <si>
     <r>
+      <t xml:space="preserve">Создать проект vite + </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>vue3</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Создать проект </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>vite + [...]</t>
+    </r>
+  </si>
+  <si>
+    <t>npm create vue@latest</t>
+  </si>
+  <si>
+    <t>`https://github.com/vuejs/create-vue</t>
+  </si>
+  <si>
+    <r>
       <t xml:space="preserve">scripts": {
     "dev": "vite --mode development",
     "build": "export NODE_OPTIONS=--openssl-legacy-provider &amp;&amp; vite build </t>
@@ -1055,8 +1080,30 @@
         <charset val="204"/>
         <scheme val="minor"/>
       </rPr>
+      <t xml:space="preserve">",
+    "electronbuilddev": "vite build </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>--mode electrondev</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>",
-    "electronbuilddev": "vite build --mode electrondev",
     "electronbuildprod": "vite build --mode electronprod",
     "electron": "electron .",
     "dist": "electron-builder --win --x64"
@@ -1065,7 +1112,31 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">Создать проект vite + </t>
+      <t xml:space="preserve">const EnvPlugin = {
+  </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>install</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(</t>
     </r>
     <r>
       <rPr>
@@ -1077,12 +1148,19 @@
         <charset val="204"/>
         <scheme val="minor"/>
       </rPr>
-      <t>vue3</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Создать проект </t>
+      <t>Vue</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">) {
+    </t>
     </r>
     <r>
       <rPr>
@@ -1094,26 +1172,669 @@
         <charset val="204"/>
         <scheme val="minor"/>
       </rPr>
-      <t>vite + [...]</t>
-    </r>
-  </si>
-  <si>
-    <t>npm create vue@latest</t>
-  </si>
-  <si>
-    <t>`https://github.com/vuejs/create-vue</t>
+      <t>Vue.prototype.$env</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> = {
+      isLocalProxy: import.meta.env.VITE_LOCALPROXY,
+      isElectronProxy: import.meta.env.VITE_ELECTRON_PROXY,
+      pathToBuild: import.meta.env.VITE_PAT_TO_BUILD,
+      apiProxy: import.meta.env.VITE_API_PROXY,
+      socketProxy: import.meta.env.VITE_SOCKET_PROXY,
+      fileLoaderPath: import.meta.env.VITE_FILE_LOAD,
+    }
+  }
+}
+export default EnvPlugin</t>
+    </r>
+  </si>
+  <si>
+    <t>main.js</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">import </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>EnvPlugin</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> from './plugins/env.js'
+Vue.use(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>EnvPlugin</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>);</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">// plugins/env.js
+export default {
+  install(app) {
+    </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>app.config.globalProperties.$env</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> = {
+      isLocalProxy: import.meta.env.VITE_LOCALPROXY,
+      // ... остальные переменные
+    }
+  }
+}</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">import </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>EnvPlugin</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> from './plugins/env'
+const app = createApp(App)
+app.use(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>EnvPlugin</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)
+app.mount('#app')</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Способ!</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> plugin</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Способ!</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Vite config</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>console.log(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>__API_URL__</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>) // Работает везде</t>
+    </r>
+  </si>
+  <si>
+    <t>vite.config.js</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">export default defineConfig({
+  define: {
+    // Преобразуем env-переменные в константы (доступны везде)
+   </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> __API_URL__</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: JSON.stringify(process.env.VITE_API_PROXY),
+  }
+})</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Важные нюансы</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+1 В Vite доступны ТОЛЬКО переменные с префиксом </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>VITE_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+2 Переменные окружения всегда </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>строки</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Способ!</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Composable</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">// composables/useEnv.js
+export const </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>useEnv</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> = () =&gt; {
+  const </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>env</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> = {
+    isLocalProxy: import.meta.env.VITE_LOCALPROXY === 'true',
+    isElectronProxy: import.meta.env.VITE_ELECTRON_PROXY === 'true',
+    pathToBuild: import.meta.env.VITE_PAT_TO_BUILD || '',
+    apiProxy: import.meta.env.VITE_API_PROXY || '',
+    socketProxy: import.meta.env.VITE_SOCKET_PROXY || '',
+    fileLoaderPath: import.meta.env.VITE_FILE_LOAD || '',
+    storagePublicUrl: import.meta.env.VITE_STORAGE_PUBLIC_URL || '',
+    nodeEnv: import.meta.env.VITE_NODE_ENV || 'development',
+  }
+  return </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>env</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+}</t>
+    </r>
+  </si>
+  <si>
+    <t>в компоненте</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">&lt;script setup&gt;
+import { </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>useEnv</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> } from '@/composables/useEnv'
+const { apiProxy, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>isLocalProxy</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> } = </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>useEnv()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+// Теперь isLocalProxy — это boolean, а не строка
+if (isLocalProxy) {
+  console.log('Работаем локально!')
+}
+&lt;/script&gt;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">import </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Vue</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> from 'vue';
+this.$http.post(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>this.$env.apiProxy</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> + '/auth/login', {
+          username: this.username, 
+          password: hash, 
+          key: !this.username.isEmpty() &amp;&amp; !this.password.isEmpty() ? null : key, 
+          type: !this.username.isEmpty() &amp;&amp; !this.password.isEmpty() ? null : type,
+        })</t>
+    </r>
+  </si>
+  <si>
+    <t>Шаг 1</t>
+  </si>
+  <si>
+    <t>Шаг 2</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Доступ к переменным окружения в </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>vite.config.js</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Доступ к переменным окружения в </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>проекте</t>
+    </r>
+  </si>
+  <si>
+    <t>Шаг 3</t>
+  </si>
+  <si>
+    <t>Шаг 4</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="21" x14ac:knownFonts="1">
+  <fonts count="22" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1279,7 +2000,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1316,6 +2037,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -1328,9 +2055,9 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -1338,47 +2065,47 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="12" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="13" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="9" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="10" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="12" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="8" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="14" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
     <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
@@ -1387,22 +2114,40 @@
     <xf numFmtId="49" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="8" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="13" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1429,13 +2174,13 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>167999</xdr:colOff>
-      <xdr:row>15</xdr:row>
+      <xdr:row>26</xdr:row>
       <xdr:rowOff>58239</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>1502858</xdr:colOff>
-      <xdr:row>15</xdr:row>
+      <xdr:row>26</xdr:row>
       <xdr:rowOff>4857751</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1814,20 +2559,20 @@
     </row>
     <row r="7" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B7" s="24"/>
       <c r="C7" s="2" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D7" s="24" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="S7" s="2"/>
     </row>
     <row r="8" spans="1:21" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>46</v>
@@ -1839,7 +2584,7 @@
     </row>
     <row r="9" spans="1:21" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B9" s="13" t="s">
         <v>50</v>
@@ -2217,7 +2962,7 @@
       <c r="D54" s="10"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="18" type="noConversion"/>
+  <phoneticPr fontId="19" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="10" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
@@ -2228,7 +2973,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:AA75"/>
+  <dimension ref="A2:AA86"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="36" style="1" customWidth="1"/>
@@ -2259,188 +3004,62 @@
     <col min="28" max="16384" width="8.77734375" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="5"/>
-      <c r="C2" s="6"/>
-      <c r="D2" s="7"/>
-      <c r="G2" s="8"/>
-      <c r="P2" s="8"/>
-      <c r="Q2" s="8"/>
-      <c r="R2" s="8"/>
-      <c r="T2" s="9"/>
-      <c r="U2" s="8"/>
+    <row r="2" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A2" s="22" t="s">
+        <v>75</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>102</v>
+      </c>
     </row>
     <row r="3" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="C3" s="25" t="s">
+      <c r="A3" s="22" t="s">
+        <v>71</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="4" spans="1:27" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A4" s="29" t="s">
+        <v>105</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="5" spans="1:27" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A5" s="29" t="s">
+        <v>104</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="7" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="5"/>
+      <c r="C7" s="6"/>
+      <c r="D7" s="7"/>
+      <c r="G7" s="8"/>
+      <c r="P7" s="8"/>
+      <c r="Q7" s="8"/>
+      <c r="R7" s="8"/>
+      <c r="T7" s="9"/>
+      <c r="U7" s="8"/>
+    </row>
+    <row r="8" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="C8" s="25" t="s">
         <v>58</v>
       </c>
-      <c r="S3" s="2"/>
-    </row>
-    <row r="4" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="22" t="s">
-        <v>76</v>
-      </c>
-      <c r="B4" s="10"/>
-      <c r="C4" s="1"/>
-      <c r="D4" s="10"/>
-      <c r="F4" s="1"/>
-      <c r="G4" s="2"/>
-      <c r="H4" s="1"/>
-      <c r="I4" s="1"/>
-      <c r="J4" s="1"/>
-      <c r="K4" s="1"/>
-      <c r="L4" s="1"/>
-      <c r="M4" s="1"/>
-      <c r="N4" s="1"/>
-      <c r="O4" s="1"/>
-      <c r="P4" s="2"/>
-      <c r="Q4" s="2"/>
-      <c r="R4" s="2"/>
-      <c r="S4" s="1"/>
-      <c r="T4"/>
-      <c r="U4" s="2"/>
-      <c r="V4" s="1"/>
-      <c r="W4" s="1"/>
-      <c r="X4" s="1"/>
-      <c r="Y4" s="1"/>
-      <c r="Z4" s="1"/>
-      <c r="AA4" s="1"/>
-    </row>
-    <row r="5" spans="1:27" s="4" customFormat="1" ht="158.4" x14ac:dyDescent="0.3">
-      <c r="A5" s="10"/>
-      <c r="B5" s="10"/>
-      <c r="C5" s="23" t="s">
-        <v>82</v>
-      </c>
-      <c r="D5" s="10"/>
-      <c r="F5" s="1"/>
-      <c r="G5" s="2"/>
-      <c r="H5" s="1"/>
-      <c r="I5" s="1"/>
-      <c r="J5" s="1"/>
-      <c r="K5" s="1"/>
-      <c r="L5" s="1"/>
-      <c r="M5" s="1"/>
-      <c r="N5" s="1"/>
-      <c r="O5" s="1"/>
-      <c r="P5" s="2"/>
-      <c r="Q5" s="2"/>
-      <c r="R5" s="2"/>
-      <c r="S5" s="1"/>
-      <c r="T5"/>
-      <c r="U5" s="2"/>
-      <c r="V5" s="1"/>
-      <c r="W5" s="1"/>
-      <c r="X5" s="1"/>
-      <c r="Y5" s="1"/>
-      <c r="Z5" s="1"/>
-      <c r="AA5" s="1"/>
-    </row>
-    <row r="6" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="22" t="s">
-        <v>71</v>
-      </c>
-      <c r="B6" s="21"/>
-      <c r="C6" s="21"/>
-      <c r="D6" s="21"/>
-      <c r="F6" s="1"/>
-      <c r="G6" s="2"/>
-      <c r="H6" s="1"/>
-      <c r="I6" s="1"/>
-      <c r="J6" s="1"/>
-      <c r="K6" s="1"/>
-      <c r="L6" s="1"/>
-      <c r="M6" s="1"/>
-      <c r="N6" s="1"/>
-      <c r="O6" s="1"/>
-      <c r="P6" s="2"/>
-      <c r="Q6" s="2"/>
-      <c r="R6" s="2"/>
-      <c r="S6" s="1"/>
-      <c r="T6"/>
-      <c r="U6" s="2"/>
-      <c r="V6" s="1"/>
-      <c r="W6" s="1"/>
-      <c r="X6" s="1"/>
-      <c r="Y6" s="1"/>
-      <c r="Z6" s="1"/>
-      <c r="AA6" s="1"/>
-    </row>
-    <row r="7" spans="1:27" s="4" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A7" s="21"/>
-      <c r="B7" s="21" t="s">
-        <v>59</v>
-      </c>
-      <c r="C7" s="21" t="s">
-        <v>60</v>
-      </c>
-      <c r="D7" s="21"/>
-      <c r="F7" s="1"/>
-      <c r="G7" s="2"/>
-      <c r="H7" s="1"/>
-      <c r="I7" s="1"/>
-      <c r="J7" s="1"/>
-      <c r="K7" s="1"/>
-      <c r="L7" s="1"/>
-      <c r="M7" s="1"/>
-      <c r="N7" s="1"/>
-      <c r="O7" s="1"/>
-      <c r="P7" s="2"/>
-      <c r="Q7" s="2"/>
-      <c r="R7" s="2"/>
-      <c r="S7" s="1"/>
-      <c r="T7"/>
-      <c r="U7" s="2"/>
-      <c r="V7" s="1"/>
-      <c r="W7" s="1"/>
-      <c r="X7" s="1"/>
-      <c r="Y7" s="1"/>
-      <c r="Z7" s="1"/>
-      <c r="AA7" s="1"/>
-    </row>
-    <row r="8" spans="1:27" s="4" customFormat="1" ht="72" x14ac:dyDescent="0.3">
-      <c r="A8" s="21" t="s">
-        <v>61</v>
-      </c>
-      <c r="B8" s="21" t="s">
-        <v>58</v>
-      </c>
-      <c r="C8" s="21" t="s">
-        <v>62</v>
-      </c>
-      <c r="D8" s="21"/>
-      <c r="F8" s="1"/>
-      <c r="G8" s="2"/>
-      <c r="H8" s="1"/>
-      <c r="I8" s="1"/>
-      <c r="J8" s="1"/>
-      <c r="K8" s="1"/>
-      <c r="L8" s="1"/>
-      <c r="M8" s="1"/>
-      <c r="N8" s="1"/>
-      <c r="O8" s="1"/>
-      <c r="P8" s="2"/>
-      <c r="Q8" s="2"/>
-      <c r="R8" s="2"/>
-      <c r="S8" s="1"/>
-      <c r="T8"/>
-      <c r="U8" s="2"/>
-      <c r="V8" s="1"/>
-      <c r="W8" s="1"/>
-      <c r="X8" s="1"/>
-      <c r="Y8" s="1"/>
-      <c r="Z8" s="1"/>
-      <c r="AA8" s="1"/>
-    </row>
-    <row r="9" spans="1:27" s="4" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A9" s="21" t="s">
-        <v>63</v>
-      </c>
-      <c r="B9" s="21"/>
-      <c r="C9" s="21" t="s">
-        <v>64</v>
-      </c>
-      <c r="D9" s="21"/>
+      <c r="S8" s="2"/>
+    </row>
+    <row r="9" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="22" t="s">
+        <v>75</v>
+      </c>
+      <c r="B9" s="10"/>
+      <c r="C9" s="1"/>
+      <c r="D9" s="10"/>
       <c r="F9" s="1"/>
       <c r="G9" s="2"/>
       <c r="H9" s="1"/>
@@ -2464,15 +3083,15 @@
       <c r="Z9" s="1"/>
       <c r="AA9" s="1"/>
     </row>
-    <row r="10" spans="1:27" s="4" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A10" s="21" t="s">
-        <v>65</v>
-      </c>
-      <c r="B10" s="21"/>
-      <c r="C10" s="21" t="s">
-        <v>66</v>
-      </c>
-      <c r="D10" s="21"/>
+    <row r="10" spans="1:27" s="4" customFormat="1" ht="158.4" x14ac:dyDescent="0.3">
+      <c r="A10" s="10"/>
+      <c r="B10" s="27" t="s">
+        <v>96</v>
+      </c>
+      <c r="C10" s="23" t="s">
+        <v>85</v>
+      </c>
+      <c r="D10" s="10"/>
       <c r="F10" s="1"/>
       <c r="G10" s="2"/>
       <c r="H10" s="1"/>
@@ -2496,14 +3115,12 @@
       <c r="Z10" s="1"/>
       <c r="AA10" s="1"/>
     </row>
-    <row r="11" spans="1:27" s="4" customFormat="1" ht="129.6" x14ac:dyDescent="0.3">
-      <c r="A11" s="21" t="s">
-        <v>67</v>
+    <row r="11" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="22" t="s">
+        <v>71</v>
       </c>
       <c r="B11" s="21"/>
-      <c r="C11" s="21" t="s">
-        <v>68</v>
-      </c>
+      <c r="C11" s="21"/>
       <c r="D11" s="21"/>
       <c r="F11" s="1"/>
       <c r="G11" s="2"/>
@@ -2528,13 +3145,13 @@
       <c r="Z11" s="1"/>
       <c r="AA11" s="1"/>
     </row>
-    <row r="12" spans="1:27" s="4" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A12" s="21" t="s">
-        <v>69</v>
-      </c>
-      <c r="B12" s="21"/>
+    <row r="12" spans="1:27" s="4" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A12" s="21"/>
+      <c r="B12" s="21" t="s">
+        <v>59</v>
+      </c>
       <c r="C12" s="21" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="D12" s="21"/>
       <c r="F12" s="1"/>
@@ -2560,15 +3177,17 @@
       <c r="Z12" s="1"/>
       <c r="AA12" s="1"/>
     </row>
-    <row r="13" spans="1:27" s="4" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A13" s="22" t="s">
-        <v>72</v>
+    <row r="13" spans="1:27" s="4" customFormat="1" ht="72" x14ac:dyDescent="0.3">
+      <c r="A13" s="26" t="s">
+        <v>61</v>
       </c>
       <c r="B13" s="21" t="s">
-        <v>73</v>
-      </c>
-      <c r="C13" s="21"/>
-      <c r="D13" s="10"/>
+        <v>58</v>
+      </c>
+      <c r="C13" s="21" t="s">
+        <v>62</v>
+      </c>
+      <c r="D13" s="21"/>
       <c r="F13" s="1"/>
       <c r="G13" s="2"/>
       <c r="H13" s="1"/>
@@ -2592,15 +3211,15 @@
       <c r="Z13" s="1"/>
       <c r="AA13" s="1"/>
     </row>
-    <row r="14" spans="1:27" s="4" customFormat="1" ht="201.6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:27" s="4" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A14" s="21" t="s">
-        <v>74</v>
+        <v>63</v>
       </c>
       <c r="B14" s="21"/>
       <c r="C14" s="21" t="s">
-        <v>75</v>
-      </c>
-      <c r="D14" s="10"/>
+        <v>64</v>
+      </c>
+      <c r="D14" s="21"/>
       <c r="F14" s="1"/>
       <c r="G14" s="2"/>
       <c r="H14" s="1"/>
@@ -2624,14 +3243,14 @@
       <c r="Z14" s="1"/>
       <c r="AA14" s="1"/>
     </row>
-    <row r="15" spans="1:27" s="4" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A15" s="22" t="s">
-        <v>72</v>
-      </c>
-      <c r="B15" s="21" t="s">
-        <v>77</v>
-      </c>
-      <c r="C15" s="21"/>
+    <row r="15" spans="1:27" s="4" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A15" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="B15" s="21"/>
+      <c r="C15" s="21" t="s">
+        <v>66</v>
+      </c>
       <c r="D15" s="21"/>
       <c r="F15" s="1"/>
       <c r="G15" s="2"/>
@@ -2656,13 +3275,13 @@
       <c r="Z15" s="1"/>
       <c r="AA15" s="1"/>
     </row>
-    <row r="16" spans="1:27" s="4" customFormat="1" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A16" s="21"/>
-      <c r="B16" s="21" t="s">
-        <v>78</v>
-      </c>
+    <row r="16" spans="1:27" s="4" customFormat="1" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="A16" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="B16" s="21"/>
       <c r="C16" s="21" t="s">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="D16" s="21"/>
       <c r="F16" s="1"/>
@@ -2688,13 +3307,13 @@
       <c r="Z16" s="1"/>
       <c r="AA16" s="1"/>
     </row>
-    <row r="17" spans="1:27" s="4" customFormat="1" ht="201.6" x14ac:dyDescent="0.3">
-      <c r="A17" s="21"/>
-      <c r="B17" s="21" t="s">
-        <v>80</v>
-      </c>
+    <row r="17" spans="1:27" s="4" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A17" s="21" t="s">
+        <v>69</v>
+      </c>
+      <c r="B17" s="21"/>
       <c r="C17" s="21" t="s">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="D17" s="21"/>
       <c r="F17" s="1"/>
@@ -2720,11 +3339,15 @@
       <c r="Z17" s="1"/>
       <c r="AA17" s="1"/>
     </row>
-    <row r="18" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="10"/>
-      <c r="B18" s="10"/>
-      <c r="C18" s="10"/>
-      <c r="D18" s="10"/>
+    <row r="18" spans="1:27" s="4" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A18" s="22" t="s">
+        <v>72</v>
+      </c>
+      <c r="B18" s="21" t="s">
+        <v>73</v>
+      </c>
+      <c r="C18" s="21"/>
+      <c r="D18" s="21"/>
       <c r="F18" s="1"/>
       <c r="G18" s="2"/>
       <c r="H18" s="1"/>
@@ -2748,67 +3371,40 @@
       <c r="Z18" s="1"/>
       <c r="AA18" s="1"/>
     </row>
-    <row r="19" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="10"/>
-      <c r="B19" s="10"/>
-      <c r="C19" s="10"/>
-      <c r="D19" s="10"/>
-      <c r="F19" s="1"/>
-      <c r="G19" s="2"/>
-      <c r="H19" s="1"/>
-      <c r="I19" s="1"/>
-      <c r="J19" s="1"/>
-      <c r="K19" s="1"/>
-      <c r="L19" s="1"/>
-      <c r="M19" s="1"/>
-      <c r="N19" s="1"/>
-      <c r="O19" s="1"/>
-      <c r="P19" s="2"/>
-      <c r="Q19" s="2"/>
-      <c r="R19" s="2"/>
-      <c r="S19" s="1"/>
-      <c r="T19"/>
-      <c r="U19" s="2"/>
-      <c r="V19" s="1"/>
-      <c r="W19" s="1"/>
-      <c r="X19" s="1"/>
-      <c r="Y19" s="1"/>
-      <c r="Z19" s="1"/>
-      <c r="AA19" s="1"/>
-    </row>
-    <row r="20" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="10"/>
-      <c r="B20" s="10"/>
-      <c r="C20" s="10"/>
-      <c r="D20" s="10"/>
-      <c r="F20" s="1"/>
-      <c r="G20" s="2"/>
-      <c r="H20" s="1"/>
-      <c r="I20" s="1"/>
-      <c r="J20" s="1"/>
-      <c r="K20" s="1"/>
-      <c r="L20" s="1"/>
-      <c r="M20" s="1"/>
-      <c r="N20" s="1"/>
-      <c r="O20" s="1"/>
-      <c r="P20" s="2"/>
-      <c r="Q20" s="2"/>
-      <c r="R20" s="2"/>
-      <c r="S20" s="1"/>
-      <c r="T20"/>
-      <c r="U20" s="2"/>
-      <c r="V20" s="1"/>
-      <c r="W20" s="1"/>
-      <c r="X20" s="1"/>
-      <c r="Y20" s="1"/>
-      <c r="Z20" s="1"/>
-      <c r="AA20" s="1"/>
+    <row r="19" spans="1:27" s="21" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="30" t="s">
+        <v>97</v>
+      </c>
+      <c r="B19" s="28" t="s">
+        <v>99</v>
+      </c>
+      <c r="C19" s="28" t="s">
+        <v>53</v>
+      </c>
+      <c r="E19" s="31"/>
+    </row>
+    <row r="20" spans="1:27" s="21" customFormat="1" ht="216" x14ac:dyDescent="0.3">
+      <c r="B20" s="27" t="s">
+        <v>100</v>
+      </c>
+      <c r="C20" s="27" t="s">
+        <v>98</v>
+      </c>
+      <c r="E20" s="31"/>
     </row>
     <row r="21" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="10"/>
-      <c r="B21" s="10"/>
-      <c r="C21" s="10"/>
-      <c r="D21" s="10"/>
+      <c r="A21" s="30" t="s">
+        <v>91</v>
+      </c>
+      <c r="B21" s="28" t="s">
+        <v>99</v>
+      </c>
+      <c r="C21" s="28" t="s">
+        <v>53</v>
+      </c>
+      <c r="D21" s="28" t="s">
+        <v>54</v>
+      </c>
       <c r="F21" s="1"/>
       <c r="G21" s="2"/>
       <c r="H21" s="1"/>
@@ -2832,11 +3428,19 @@
       <c r="Z21" s="1"/>
       <c r="AA21" s="1"/>
     </row>
-    <row r="22" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="10"/>
-      <c r="B22" s="10"/>
-      <c r="C22" s="10"/>
-      <c r="D22" s="10"/>
+    <row r="22" spans="1:27" s="4" customFormat="1" ht="201.6" x14ac:dyDescent="0.3">
+      <c r="A22" s="21" t="s">
+        <v>74</v>
+      </c>
+      <c r="B22" s="27" t="s">
+        <v>101</v>
+      </c>
+      <c r="C22" s="27" t="s">
+        <v>89</v>
+      </c>
+      <c r="D22" s="27" t="s">
+        <v>86</v>
+      </c>
       <c r="F22" s="1"/>
       <c r="G22" s="2"/>
       <c r="H22" s="1"/>
@@ -2860,11 +3464,17 @@
       <c r="Z22" s="1"/>
       <c r="AA22" s="1"/>
     </row>
-    <row r="23" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="10"/>
-      <c r="B23" s="10"/>
-      <c r="C23" s="10"/>
-      <c r="D23" s="10"/>
+    <row r="23" spans="1:27" s="4" customFormat="1" ht="72" x14ac:dyDescent="0.3">
+      <c r="A23" s="27" t="s">
+        <v>87</v>
+      </c>
+      <c r="B23" s="27"/>
+      <c r="C23" s="27" t="s">
+        <v>90</v>
+      </c>
+      <c r="D23" s="27" t="s">
+        <v>88</v>
+      </c>
       <c r="F23" s="1"/>
       <c r="G23" s="2"/>
       <c r="H23" s="1"/>
@@ -2889,10 +3499,12 @@
       <c r="AA23" s="1"/>
     </row>
     <row r="24" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="10"/>
-      <c r="B24" s="10"/>
-      <c r="C24" s="10"/>
-      <c r="D24" s="10"/>
+      <c r="A24" s="30" t="s">
+        <v>92</v>
+      </c>
+      <c r="B24" s="21"/>
+      <c r="C24" s="27"/>
+      <c r="D24" s="27"/>
       <c r="F24" s="1"/>
       <c r="G24" s="2"/>
       <c r="H24" s="1"/>
@@ -2916,11 +3528,17 @@
       <c r="Z24" s="1"/>
       <c r="AA24" s="1"/>
     </row>
-    <row r="25" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="10"/>
-      <c r="B25" s="10"/>
-      <c r="C25" s="10"/>
-      <c r="D25" s="10"/>
+    <row r="25" spans="1:27" s="4" customFormat="1" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A25" s="27" t="s">
+        <v>94</v>
+      </c>
+      <c r="B25" s="21"/>
+      <c r="C25" s="27" t="s">
+        <v>95</v>
+      </c>
+      <c r="D25" s="27" t="s">
+        <v>93</v>
+      </c>
       <c r="F25" s="1"/>
       <c r="G25" s="2"/>
       <c r="H25" s="1"/>
@@ -2944,11 +3562,15 @@
       <c r="Z25" s="1"/>
       <c r="AA25" s="1"/>
     </row>
-    <row r="26" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="10"/>
-      <c r="B26" s="10"/>
-      <c r="C26" s="10"/>
-      <c r="D26" s="10"/>
+    <row r="26" spans="1:27" s="4" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A26" s="22" t="s">
+        <v>72</v>
+      </c>
+      <c r="B26" s="21" t="s">
+        <v>76</v>
+      </c>
+      <c r="C26" s="21"/>
+      <c r="D26" s="21"/>
       <c r="F26" s="1"/>
       <c r="G26" s="2"/>
       <c r="H26" s="1"/>
@@ -2972,11 +3594,15 @@
       <c r="Z26" s="1"/>
       <c r="AA26" s="1"/>
     </row>
-    <row r="27" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="10"/>
-      <c r="B27" s="10"/>
-      <c r="C27" s="10"/>
-      <c r="D27" s="10"/>
+    <row r="27" spans="1:27" s="4" customFormat="1" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A27" s="21"/>
+      <c r="B27" s="21" t="s">
+        <v>77</v>
+      </c>
+      <c r="C27" s="21" t="s">
+        <v>78</v>
+      </c>
+      <c r="D27" s="21"/>
       <c r="F27" s="1"/>
       <c r="G27" s="2"/>
       <c r="H27" s="1"/>
@@ -3000,11 +3626,15 @@
       <c r="Z27" s="1"/>
       <c r="AA27" s="1"/>
     </row>
-    <row r="28" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="10"/>
-      <c r="B28" s="10"/>
-      <c r="C28" s="10"/>
-      <c r="D28" s="10"/>
+    <row r="28" spans="1:27" s="4" customFormat="1" ht="201.6" x14ac:dyDescent="0.3">
+      <c r="A28" s="21"/>
+      <c r="B28" s="21" t="s">
+        <v>79</v>
+      </c>
+      <c r="C28" s="21" t="s">
+        <v>80</v>
+      </c>
+      <c r="D28" s="21"/>
       <c r="F28" s="1"/>
       <c r="G28" s="2"/>
       <c r="H28" s="1"/>
@@ -4344,7 +4974,316 @@
       <c r="Z75" s="1"/>
       <c r="AA75" s="1"/>
     </row>
+    <row r="76" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A76" s="10"/>
+      <c r="B76" s="10"/>
+      <c r="C76" s="10"/>
+      <c r="D76" s="10"/>
+      <c r="F76" s="1"/>
+      <c r="G76" s="2"/>
+      <c r="H76" s="1"/>
+      <c r="I76" s="1"/>
+      <c r="J76" s="1"/>
+      <c r="K76" s="1"/>
+      <c r="L76" s="1"/>
+      <c r="M76" s="1"/>
+      <c r="N76" s="1"/>
+      <c r="O76" s="1"/>
+      <c r="P76" s="2"/>
+      <c r="Q76" s="2"/>
+      <c r="R76" s="2"/>
+      <c r="S76" s="1"/>
+      <c r="T76"/>
+      <c r="U76" s="2"/>
+      <c r="V76" s="1"/>
+      <c r="W76" s="1"/>
+      <c r="X76" s="1"/>
+      <c r="Y76" s="1"/>
+      <c r="Z76" s="1"/>
+      <c r="AA76" s="1"/>
+    </row>
+    <row r="77" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A77" s="10"/>
+      <c r="B77" s="10"/>
+      <c r="C77" s="10"/>
+      <c r="D77" s="10"/>
+      <c r="F77" s="1"/>
+      <c r="G77" s="2"/>
+      <c r="H77" s="1"/>
+      <c r="I77" s="1"/>
+      <c r="J77" s="1"/>
+      <c r="K77" s="1"/>
+      <c r="L77" s="1"/>
+      <c r="M77" s="1"/>
+      <c r="N77" s="1"/>
+      <c r="O77" s="1"/>
+      <c r="P77" s="2"/>
+      <c r="Q77" s="2"/>
+      <c r="R77" s="2"/>
+      <c r="S77" s="1"/>
+      <c r="T77"/>
+      <c r="U77" s="2"/>
+      <c r="V77" s="1"/>
+      <c r="W77" s="1"/>
+      <c r="X77" s="1"/>
+      <c r="Y77" s="1"/>
+      <c r="Z77" s="1"/>
+      <c r="AA77" s="1"/>
+    </row>
+    <row r="78" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A78" s="10"/>
+      <c r="B78" s="10"/>
+      <c r="C78" s="10"/>
+      <c r="D78" s="10"/>
+      <c r="F78" s="1"/>
+      <c r="G78" s="2"/>
+      <c r="H78" s="1"/>
+      <c r="I78" s="1"/>
+      <c r="J78" s="1"/>
+      <c r="K78" s="1"/>
+      <c r="L78" s="1"/>
+      <c r="M78" s="1"/>
+      <c r="N78" s="1"/>
+      <c r="O78" s="1"/>
+      <c r="P78" s="2"/>
+      <c r="Q78" s="2"/>
+      <c r="R78" s="2"/>
+      <c r="S78" s="1"/>
+      <c r="T78"/>
+      <c r="U78" s="2"/>
+      <c r="V78" s="1"/>
+      <c r="W78" s="1"/>
+      <c r="X78" s="1"/>
+      <c r="Y78" s="1"/>
+      <c r="Z78" s="1"/>
+      <c r="AA78" s="1"/>
+    </row>
+    <row r="79" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A79" s="10"/>
+      <c r="B79" s="10"/>
+      <c r="C79" s="10"/>
+      <c r="D79" s="10"/>
+      <c r="F79" s="1"/>
+      <c r="G79" s="2"/>
+      <c r="H79" s="1"/>
+      <c r="I79" s="1"/>
+      <c r="J79" s="1"/>
+      <c r="K79" s="1"/>
+      <c r="L79" s="1"/>
+      <c r="M79" s="1"/>
+      <c r="N79" s="1"/>
+      <c r="O79" s="1"/>
+      <c r="P79" s="2"/>
+      <c r="Q79" s="2"/>
+      <c r="R79" s="2"/>
+      <c r="S79" s="1"/>
+      <c r="T79"/>
+      <c r="U79" s="2"/>
+      <c r="V79" s="1"/>
+      <c r="W79" s="1"/>
+      <c r="X79" s="1"/>
+      <c r="Y79" s="1"/>
+      <c r="Z79" s="1"/>
+      <c r="AA79" s="1"/>
+    </row>
+    <row r="80" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A80" s="10"/>
+      <c r="B80" s="10"/>
+      <c r="C80" s="10"/>
+      <c r="D80" s="10"/>
+      <c r="F80" s="1"/>
+      <c r="G80" s="2"/>
+      <c r="H80" s="1"/>
+      <c r="I80" s="1"/>
+      <c r="J80" s="1"/>
+      <c r="K80" s="1"/>
+      <c r="L80" s="1"/>
+      <c r="M80" s="1"/>
+      <c r="N80" s="1"/>
+      <c r="O80" s="1"/>
+      <c r="P80" s="2"/>
+      <c r="Q80" s="2"/>
+      <c r="R80" s="2"/>
+      <c r="S80" s="1"/>
+      <c r="T80"/>
+      <c r="U80" s="2"/>
+      <c r="V80" s="1"/>
+      <c r="W80" s="1"/>
+      <c r="X80" s="1"/>
+      <c r="Y80" s="1"/>
+      <c r="Z80" s="1"/>
+      <c r="AA80" s="1"/>
+    </row>
+    <row r="81" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A81" s="10"/>
+      <c r="B81" s="10"/>
+      <c r="C81" s="10"/>
+      <c r="D81" s="10"/>
+      <c r="F81" s="1"/>
+      <c r="G81" s="2"/>
+      <c r="H81" s="1"/>
+      <c r="I81" s="1"/>
+      <c r="J81" s="1"/>
+      <c r="K81" s="1"/>
+      <c r="L81" s="1"/>
+      <c r="M81" s="1"/>
+      <c r="N81" s="1"/>
+      <c r="O81" s="1"/>
+      <c r="P81" s="2"/>
+      <c r="Q81" s="2"/>
+      <c r="R81" s="2"/>
+      <c r="S81" s="1"/>
+      <c r="T81"/>
+      <c r="U81" s="2"/>
+      <c r="V81" s="1"/>
+      <c r="W81" s="1"/>
+      <c r="X81" s="1"/>
+      <c r="Y81" s="1"/>
+      <c r="Z81" s="1"/>
+      <c r="AA81" s="1"/>
+    </row>
+    <row r="82" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A82" s="10"/>
+      <c r="B82" s="10"/>
+      <c r="C82" s="10"/>
+      <c r="D82" s="10"/>
+      <c r="F82" s="1"/>
+      <c r="G82" s="2"/>
+      <c r="H82" s="1"/>
+      <c r="I82" s="1"/>
+      <c r="J82" s="1"/>
+      <c r="K82" s="1"/>
+      <c r="L82" s="1"/>
+      <c r="M82" s="1"/>
+      <c r="N82" s="1"/>
+      <c r="O82" s="1"/>
+      <c r="P82" s="2"/>
+      <c r="Q82" s="2"/>
+      <c r="R82" s="2"/>
+      <c r="S82" s="1"/>
+      <c r="T82"/>
+      <c r="U82" s="2"/>
+      <c r="V82" s="1"/>
+      <c r="W82" s="1"/>
+      <c r="X82" s="1"/>
+      <c r="Y82" s="1"/>
+      <c r="Z82" s="1"/>
+      <c r="AA82" s="1"/>
+    </row>
+    <row r="83" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A83" s="10"/>
+      <c r="B83" s="10"/>
+      <c r="C83" s="10"/>
+      <c r="D83" s="10"/>
+      <c r="F83" s="1"/>
+      <c r="G83" s="2"/>
+      <c r="H83" s="1"/>
+      <c r="I83" s="1"/>
+      <c r="J83" s="1"/>
+      <c r="K83" s="1"/>
+      <c r="L83" s="1"/>
+      <c r="M83" s="1"/>
+      <c r="N83" s="1"/>
+      <c r="O83" s="1"/>
+      <c r="P83" s="2"/>
+      <c r="Q83" s="2"/>
+      <c r="R83" s="2"/>
+      <c r="S83" s="1"/>
+      <c r="T83"/>
+      <c r="U83" s="2"/>
+      <c r="V83" s="1"/>
+      <c r="W83" s="1"/>
+      <c r="X83" s="1"/>
+      <c r="Y83" s="1"/>
+      <c r="Z83" s="1"/>
+      <c r="AA83" s="1"/>
+    </row>
+    <row r="84" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A84" s="10"/>
+      <c r="B84" s="10"/>
+      <c r="C84" s="10"/>
+      <c r="D84" s="10"/>
+      <c r="F84" s="1"/>
+      <c r="G84" s="2"/>
+      <c r="H84" s="1"/>
+      <c r="I84" s="1"/>
+      <c r="J84" s="1"/>
+      <c r="K84" s="1"/>
+      <c r="L84" s="1"/>
+      <c r="M84" s="1"/>
+      <c r="N84" s="1"/>
+      <c r="O84" s="1"/>
+      <c r="P84" s="2"/>
+      <c r="Q84" s="2"/>
+      <c r="R84" s="2"/>
+      <c r="S84" s="1"/>
+      <c r="T84"/>
+      <c r="U84" s="2"/>
+      <c r="V84" s="1"/>
+      <c r="W84" s="1"/>
+      <c r="X84" s="1"/>
+      <c r="Y84" s="1"/>
+      <c r="Z84" s="1"/>
+      <c r="AA84" s="1"/>
+    </row>
+    <row r="85" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A85" s="10"/>
+      <c r="B85" s="10"/>
+      <c r="C85" s="10"/>
+      <c r="D85" s="10"/>
+      <c r="F85" s="1"/>
+      <c r="G85" s="2"/>
+      <c r="H85" s="1"/>
+      <c r="I85" s="1"/>
+      <c r="J85" s="1"/>
+      <c r="K85" s="1"/>
+      <c r="L85" s="1"/>
+      <c r="M85" s="1"/>
+      <c r="N85" s="1"/>
+      <c r="O85" s="1"/>
+      <c r="P85" s="2"/>
+      <c r="Q85" s="2"/>
+      <c r="R85" s="2"/>
+      <c r="S85" s="1"/>
+      <c r="T85"/>
+      <c r="U85" s="2"/>
+      <c r="V85" s="1"/>
+      <c r="W85" s="1"/>
+      <c r="X85" s="1"/>
+      <c r="Y85" s="1"/>
+      <c r="Z85" s="1"/>
+      <c r="AA85" s="1"/>
+    </row>
+    <row r="86" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A86" s="10"/>
+      <c r="B86" s="10"/>
+      <c r="C86" s="10"/>
+      <c r="D86" s="10"/>
+      <c r="F86" s="1"/>
+      <c r="G86" s="2"/>
+      <c r="H86" s="1"/>
+      <c r="I86" s="1"/>
+      <c r="J86" s="1"/>
+      <c r="K86" s="1"/>
+      <c r="L86" s="1"/>
+      <c r="M86" s="1"/>
+      <c r="N86" s="1"/>
+      <c r="O86" s="1"/>
+      <c r="P86" s="2"/>
+      <c r="Q86" s="2"/>
+      <c r="R86" s="2"/>
+      <c r="S86" s="1"/>
+      <c r="T86"/>
+      <c r="U86" s="2"/>
+      <c r="V86" s="1"/>
+      <c r="W86" s="1"/>
+      <c r="X86" s="1"/>
+      <c r="Y86" s="1"/>
+      <c r="Z86" s="1"/>
+      <c r="AA86" s="1"/>
+    </row>
   </sheetData>
+  <phoneticPr fontId="19" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="10" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
   <drawing r:id="rId2"/>

--- a/4 четверть_19_JavaScript_vite.xlsx
+++ b/4 четверть_19_JavaScript_vite.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AlexServHW\Desktop\GB_Developer_Workbook\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E0D2B5D-19E2-4D58-81D3-58322A654FFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F81B1623-4372-43AF-BD68-500A2C1FFFDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="vite" sheetId="15" r:id="rId1"/>
@@ -219,67 +219,6 @@
   </si>
   <si>
     <t>template названия</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">npm create vite@latest </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF7030A0"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>my-vue-app</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF7030A0"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>--</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> --template </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF7030A0"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>vue</t>
-    </r>
   </si>
   <si>
     <r>
@@ -1816,17 +1755,153 @@
   <si>
     <t>Шаг 4</t>
   </si>
+  <si>
+    <r>
+      <t xml:space="preserve">npm create vite@latest </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>my-vue-app</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>--</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> --template </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>vue</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> //my-vue-app folder</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">npm create vite@latest </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">-- --template vue </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> //current directory</t>
+    </r>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="22" x14ac:knownFonts="1">
+  <fonts count="24" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1999,6 +2074,14 @@
       <charset val="204"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="8">
     <fill>
@@ -2055,7 +2138,7 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -2065,47 +2148,47 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="13" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="14" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="10" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="11" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="12" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="13" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="8" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="9" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="15" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
     <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="14" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="8" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
@@ -2114,40 +2197,40 @@
     <xf numFmtId="49" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="8" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="9" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="14" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="13" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2540,17 +2623,17 @@
     </row>
     <row r="5" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A5" s="17" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C5" s="2"/>
       <c r="S5" s="2"/>
     </row>
     <row r="6" spans="1:21" ht="72" x14ac:dyDescent="0.3">
       <c r="A6" s="13" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>45</v>
@@ -2559,47 +2642,47 @@
     </row>
     <row r="7" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B7" s="24"/>
       <c r="C7" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D7" s="24" t="s">
         <v>83</v>
-      </c>
-      <c r="D7" s="24" t="s">
-        <v>84</v>
       </c>
       <c r="S7" s="2"/>
     </row>
     <row r="8" spans="1:21" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>46</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="S8" s="2"/>
     </row>
     <row r="9" spans="1:21" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B9" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="D9" s="13" t="s">
         <v>50</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="D9" s="13" t="s">
-        <v>51</v>
       </c>
       <c r="S9" s="2"/>
     </row>
     <row r="10" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A10" s="18" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C10" s="2"/>
       <c r="S10" s="2"/>
@@ -2607,16 +2690,16 @@
     <row r="11" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A11" s="2"/>
       <c r="B11" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C11" s="16" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="S11" s="2"/>
     </row>
     <row r="12" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A12" s="19" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C12" s="16"/>
       <c r="S12" s="2"/>
@@ -2962,7 +3045,7 @@
       <c r="D54" s="10"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="19" type="noConversion"/>
+  <phoneticPr fontId="20" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="10" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
@@ -3006,34 +3089,34 @@
   <sheetData>
     <row r="2" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A2" s="22" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="3" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A3" s="22" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="4" spans="1:27" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A4" s="29" t="s">
+        <v>104</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>105</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>106</v>
       </c>
     </row>
     <row r="5" spans="1:27" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A5" s="29" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="7" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.3">
@@ -3049,13 +3132,13 @@
     </row>
     <row r="8" spans="1:27" x14ac:dyDescent="0.3">
       <c r="C8" s="25" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="S8" s="2"/>
     </row>
     <row r="9" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A9" s="22" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B9" s="10"/>
       <c r="C9" s="1"/>
@@ -3086,10 +3169,10 @@
     <row r="10" spans="1:27" s="4" customFormat="1" ht="158.4" x14ac:dyDescent="0.3">
       <c r="A10" s="10"/>
       <c r="B10" s="27" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C10" s="23" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D10" s="10"/>
       <c r="F10" s="1"/>
@@ -3117,7 +3200,7 @@
     </row>
     <row r="11" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A11" s="22" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B11" s="21"/>
       <c r="C11" s="21"/>
@@ -3148,10 +3231,10 @@
     <row r="12" spans="1:27" s="4" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A12" s="21"/>
       <c r="B12" s="21" t="s">
+        <v>58</v>
+      </c>
+      <c r="C12" s="21" t="s">
         <v>59</v>
-      </c>
-      <c r="C12" s="21" t="s">
-        <v>60</v>
       </c>
       <c r="D12" s="21"/>
       <c r="F12" s="1"/>
@@ -3179,13 +3262,13 @@
     </row>
     <row r="13" spans="1:27" s="4" customFormat="1" ht="72" x14ac:dyDescent="0.3">
       <c r="A13" s="26" t="s">
+        <v>60</v>
+      </c>
+      <c r="B13" s="21" t="s">
+        <v>57</v>
+      </c>
+      <c r="C13" s="21" t="s">
         <v>61</v>
-      </c>
-      <c r="B13" s="21" t="s">
-        <v>58</v>
-      </c>
-      <c r="C13" s="21" t="s">
-        <v>62</v>
       </c>
       <c r="D13" s="21"/>
       <c r="F13" s="1"/>
@@ -3213,11 +3296,11 @@
     </row>
     <row r="14" spans="1:27" s="4" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A14" s="21" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B14" s="21"/>
       <c r="C14" s="21" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D14" s="21"/>
       <c r="F14" s="1"/>
@@ -3245,11 +3328,11 @@
     </row>
     <row r="15" spans="1:27" s="4" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A15" s="21" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B15" s="21"/>
       <c r="C15" s="21" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D15" s="21"/>
       <c r="F15" s="1"/>
@@ -3277,11 +3360,11 @@
     </row>
     <row r="16" spans="1:27" s="4" customFormat="1" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A16" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B16" s="21"/>
       <c r="C16" s="21" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D16" s="21"/>
       <c r="F16" s="1"/>
@@ -3309,11 +3392,11 @@
     </row>
     <row r="17" spans="1:27" s="4" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A17" s="21" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B17" s="21"/>
       <c r="C17" s="21" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D17" s="21"/>
       <c r="F17" s="1"/>
@@ -3341,10 +3424,10 @@
     </row>
     <row r="18" spans="1:27" s="4" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A18" s="22" t="s">
+        <v>71</v>
+      </c>
+      <c r="B18" s="21" t="s">
         <v>72</v>
-      </c>
-      <c r="B18" s="21" t="s">
-        <v>73</v>
       </c>
       <c r="C18" s="21"/>
       <c r="D18" s="21"/>
@@ -3373,37 +3456,37 @@
     </row>
     <row r="19" spans="1:27" s="21" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A19" s="30" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B19" s="28" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C19" s="28" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E19" s="31"/>
     </row>
     <row r="20" spans="1:27" s="21" customFormat="1" ht="216" x14ac:dyDescent="0.3">
       <c r="B20" s="27" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C20" s="27" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E20" s="31"/>
     </row>
     <row r="21" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A21" s="30" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B21" s="28" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C21" s="28" t="s">
+        <v>52</v>
+      </c>
+      <c r="D21" s="28" t="s">
         <v>53</v>
-      </c>
-      <c r="D21" s="28" t="s">
-        <v>54</v>
       </c>
       <c r="F21" s="1"/>
       <c r="G21" s="2"/>
@@ -3430,16 +3513,16 @@
     </row>
     <row r="22" spans="1:27" s="4" customFormat="1" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A22" s="21" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B22" s="27" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C22" s="27" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D22" s="27" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F22" s="1"/>
       <c r="G22" s="2"/>
@@ -3466,14 +3549,14 @@
     </row>
     <row r="23" spans="1:27" s="4" customFormat="1" ht="72" x14ac:dyDescent="0.3">
       <c r="A23" s="27" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B23" s="27"/>
       <c r="C23" s="27" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D23" s="27" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F23" s="1"/>
       <c r="G23" s="2"/>
@@ -3500,7 +3583,7 @@
     </row>
     <row r="24" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A24" s="30" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B24" s="21"/>
       <c r="C24" s="27"/>
@@ -3530,14 +3613,14 @@
     </row>
     <row r="25" spans="1:27" s="4" customFormat="1" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A25" s="27" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B25" s="21"/>
       <c r="C25" s="27" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D25" s="27" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F25" s="1"/>
       <c r="G25" s="2"/>
@@ -3564,10 +3647,10 @@
     </row>
     <row r="26" spans="1:27" s="4" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A26" s="22" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B26" s="21" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C26" s="21"/>
       <c r="D26" s="21"/>
@@ -3597,10 +3680,10 @@
     <row r="27" spans="1:27" s="4" customFormat="1" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A27" s="21"/>
       <c r="B27" s="21" t="s">
+        <v>76</v>
+      </c>
+      <c r="C27" s="21" t="s">
         <v>77</v>
-      </c>
-      <c r="C27" s="21" t="s">
-        <v>78</v>
       </c>
       <c r="D27" s="21"/>
       <c r="F27" s="1"/>
@@ -3629,10 +3712,10 @@
     <row r="28" spans="1:27" s="4" customFormat="1" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A28" s="21"/>
       <c r="B28" s="21" t="s">
+        <v>78</v>
+      </c>
+      <c r="C28" s="21" t="s">
         <v>79</v>
-      </c>
-      <c r="C28" s="21" t="s">
-        <v>80</v>
       </c>
       <c r="D28" s="21"/>
       <c r="F28" s="1"/>
@@ -5283,7 +5366,7 @@
       <c r="AA86" s="1"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="19" type="noConversion"/>
+  <phoneticPr fontId="20" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="10" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
   <drawing r:id="rId2"/>
